--- a/VerveStacks_BRA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60545E26-8F74-4243-8433-3A641472431F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{101426D3-1019-4171-95E9-21BEBA6295C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1705,18 +1705,120 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_096</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 96</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_103</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 103</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_082</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 82</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_110</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 110</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_081</t>
   </si>
   <si>
@@ -1747,6 +1849,438 @@
     <t>connecting solar to buses in cluster 50</t>
   </si>
   <si>
+    <t>distr_solelc_spv_106</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 106</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_108</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 108</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_111</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 111</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_087</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 87</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_091</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 91</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_114</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 114</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_092</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 92</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_107</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 107</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_097</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 97</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_094</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 94</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_095</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 95</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_104</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 104</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_093</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 93</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_105</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 105</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_099</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 99</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_090</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 90</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_089</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 89</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_101</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 101</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_088</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 88</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_113</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 113</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_086</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 86</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_109</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 109</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_083</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 83</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_085</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 85</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_112</t>
   </si>
   <si>
@@ -1825,540 +2359,6 @@
     <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_solelc_spv_093</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 93</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_105</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 105</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_109</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 109</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_083</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 83</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_085</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 85</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_113</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 113</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_086</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 86</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_107</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 107</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_097</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 97</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_101</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 101</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_088</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 88</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_103</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 103</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_082</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 82</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_091</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 91</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_094</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 94</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_095</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 95</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_104</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 104</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_096</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 96</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_114</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 114</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_092</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 92</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_106</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 106</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_108</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 108</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_111</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 111</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_087</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 87</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_099</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 99</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_090</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 90</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_089</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 89</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_115</t>
   </si>
   <si>
@@ -2407,6 +2407,57 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500</t>
+  </si>
+  <si>
+    <t>e_BR592-500,e_BR602-500,e_BR556-500,e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500,e_BR583-500</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
+  </si>
+  <si>
+    <t>e_BR342-230,e_BR327-230,e_w307168542-230,e_BR411-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_BR411-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>e_BR283-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR787-525,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w206109551-500,e_BR662-440,e_BR639-440,e_BR732-500,e_BR673-440</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
+  </si>
+  <si>
+    <t>e_BR556-500,e_BR506-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR578-500</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR125-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
+  </si>
+  <si>
+    <t>e_BR587-500,e_BR535-500,e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_BR248-500,e_BR221-500,e_BR122-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500</t>
+  </si>
+  <si>
+    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR208-500,e_BR63-500,e_BR80-500,e_BR78-500</t>
+  </si>
+  <si>
     <t>e_BR319-230,e_BR318-230,e_BR303-230,e_BR284-500,e_BR274-500</t>
   </si>
   <si>
@@ -2425,6 +2476,201 @@
     <t>e_BR478-500,e_BR437-500,e_BR428-500,e_BR382-500,e_BR464-500,e_BR483-500,e_BR387-500,e_BR354-500,e_w954122148-500,e_w596594961-500,e_BR439-500,e_BR413-500</t>
   </si>
   <si>
+    <t>e_BR319-230</t>
+  </si>
+  <si>
+    <t>e_BR303-230,e_BR284-500,e_BR274-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_BR283-500</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR876-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR446-500,e_BR487-500</t>
+  </si>
+  <si>
+    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
+  </si>
+  <si>
+    <t>e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR487-500,e_BR435-500,e_BR367-500,e_w306104018-500</t>
+  </si>
+  <si>
+    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
+  </si>
+  <si>
+    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR300-500,e_BR433-500,e_BR437-500,e_w953014442-500,e_BR309-500</t>
+  </si>
+  <si>
+    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_w603494578-500</t>
+  </si>
+  <si>
+    <t>e_w284868411-230,e_BR327-230,e_BR315-230</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR446-500,e_BR369-500</t>
+  </si>
+  <si>
+    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
+  </si>
+  <si>
+    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
+  </si>
+  <si>
+    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500,e_w150728360-500,e_BR858-500,e_BR833-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500,e_BR125-500,e_BR246-500</t>
+  </si>
+  <si>
+    <t>e_BR571-500,e_BR558-500,e_BR535-500</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR363-500,e_BR337-500,e_BR304-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
+  </si>
+  <si>
+    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR626-440,e_w302901044-440,e_BR487-500,e_BR609-440</t>
+  </si>
+  <si>
+    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_w215284729-500,e_BR77-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR246-500,e_BR387-500,e_BR254-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR337-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>e_BR315-230,e_BR327-230,e_BR342-230,e_w307168542-230</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_w302901044-440,e_BR609-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
+  </si>
+  <si>
+    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
+  </si>
+  <si>
+    <t>e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR525-500,e_BR500-500,e_BR550-500,e_BR473-500</t>
+  </si>
+  <si>
+    <t>e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
+  </si>
+  <si>
+    <t>e_BR141-500,e_BR125-500,e_BR61-500,e_BR122-500,e_BR185-500</t>
+  </si>
+  <si>
+    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_w287374167-500</t>
+  </si>
+  <si>
+    <t>e_w287374167-500,e_BR24-500,e_w285044818-500</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440</t>
+  </si>
+  <si>
+    <t>e_BR487-500,e_BR515-500,e_w306104018-500,e_r6844204-500,e_BR490-500</t>
+  </si>
+  <si>
+    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
+  </si>
+  <si>
+    <t>e_BR270-230,e_w304646981-500</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
+  </si>
+  <si>
+    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR221-500,e_BR209-500,e_BR321-500,e_BR282-500</t>
+  </si>
+  <si>
+    <t>e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>e_BR550-500,e_BR525-500,e_BR490-500,e_BR493-500</t>
+  </si>
+  <si>
+    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_BR270-230</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR20-500</t>
+  </si>
+  <si>
+    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
+  </si>
+  <si>
+    <t>e_BR629-500,e_w537470701-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
+  </si>
+  <si>
+    <t>e_BR300-500,e_w271191830-500,e_BR310-500,e_BR184-500,e_BR309-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>e_w304646981-500,e_BR283-500,e_w287374167-500,e_w453724535-500</t>
+  </si>
+  <si>
+    <t>e_BR22-500,e_BR21-500,e_w285044818-500,e_w525253078-500</t>
+  </si>
+  <si>
+    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
+  </si>
+  <si>
+    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
+  </si>
+  <si>
+    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
+  </si>
+  <si>
     <t>e_BR319-230,e_BR318-230</t>
   </si>
   <si>
@@ -2434,9 +2680,6 @@
     <t>e_w307168542-230,e_BR342-230,e_BR283-500</t>
   </si>
   <si>
-    <t>e_w304646981-500,e_w287374167-500</t>
-  </si>
-  <si>
     <t>e_w168664395-500,e_BR371-500,e_BR446-500</t>
   </si>
   <si>
@@ -2464,249 +2707,6 @@
     <t>e_BR340-500,e_BR302-500,e_BR292-500,e_w603494578-500,e_BR204-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_BR258-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500</t>
   </si>
   <si>
-    <t>e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR315-230,e_BR327-230,e_BR342-230,e_w307168542-230</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_w302901044-440,e_BR609-440,e_BR639-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_w302931307-500,e_w174017677-440,e_BR630-440,e_BR628-440,e_w537470701-500,e_BR646-440,e_BR606-500</t>
-  </si>
-  <si>
-    <t>e_BR367-500,e_BR310-500,e_BR300-500,e_BR381-500</t>
-  </si>
-  <si>
-    <t>e_BR490-500,e_BR482-500,e_BR493-500,e_BR485-500,e_BR475-500,e_BR525-500,e_BR500-500,e_BR550-500,e_BR473-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR475-500,e_BR433-500,e_BR473-500,e_BR437-500,e_BR373-500,e_BR382-500</t>
-  </si>
-  <si>
-    <t>e_BR141-500,e_BR125-500,e_BR61-500,e_BR122-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>e_w954122148-500,e_BR462-500,e_BR439-500,e_BR499-500,e_BR430-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>e_BR535-500,e_BR499-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_BR283-500,e_w287374167-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_BR22-500,e_BR21-500,e_w285044818-500,e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_BR52-500,e_w453724535-500,e_BR181-500</t>
-  </si>
-  <si>
-    <t>e_BR181-500,e_BR171-500,e_w515552863-500,e_w215284729-500,e_BR143-500,e_BR119-500,e_BR77-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR728-440,e_BR764-440,e_w225181494-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR305-230,e_BR303-230</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_BR270-230</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_w969586211-525,e_BR984-525,e_w528904118-500,e_BR992-525</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR20-500</t>
-  </si>
-  <si>
-    <t>e_BR845-500,e_w131742617-500,e_BR802-500,e_w385000005-500,e_BR786-500</t>
-  </si>
-  <si>
-    <t>e_BR629-500,e_w537470701-500,e_BR641-500,e_w174852067-440,e_BR592-500,e_w174852067-500,e_BR602-500</t>
-  </si>
-  <si>
-    <t>e_BR300-500,e_w271191830-500,e_BR310-500,e_BR184-500,e_BR309-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>e_w304646981-500,e_w287374167-500,e_BR22-500</t>
-  </si>
-  <si>
-    <t>e_w32300871-525,e_BR803-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500,e_w150728360-500,e_BR858-500,e_BR833-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500,e_BR125-500,e_BR246-500</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR558-500,e_BR535-500</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR363-500,e_BR337-500,e_BR304-500,e_BR355-500,e_BR321-500,e_BR400-500,e_BR360-500,e_BR344-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_BR327-230,e_BR315-230,e_BR342-230</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_w168904844-230,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR221-500,e_BR209-500,e_BR321-500,e_BR282-500</t>
-  </si>
-  <si>
-    <t>e_BR342-230,e_BR327-230,e_w307168542-230,e_BR411-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_BR411-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>e_BR283-500,e_w453724535-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR787-525,e_BR657-440,e_w206109551-500,e_w125761912-500,e_BR832-500,e_w125761912-765</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w206109551-500,e_BR662-440,e_BR639-440,e_BR732-500,e_BR673-440</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR367-500,e_w306104018-500,e_BR435-500,e_BR381-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>e_BR781-500,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR728-440,e_BR670-440,e_BR650-440,e_w172071437-440,e_BR666-440,e_BR744-440,e_BR696-500,e_BR686-500,e_BR758-440,e_BR746-500,e_BR700-500,e_BR755-500,e_BR713-500,e_BR703-500,e_w539025237-440</t>
-  </si>
-  <si>
-    <t>e_BR556-500,e_BR506-500,e_BR580-500,e_BR528-500,e_BR583-500,e_BR578-500</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR125-500,e_BR49-500,e_BR122-500,e_BR42-500,e_BR51-500,e_BR72-500</t>
-  </si>
-  <si>
-    <t>e_BR587-500,e_BR535-500,e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>e_BR248-500,e_BR221-500,e_BR122-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR459-500,e_BR412-500</t>
-  </si>
-  <si>
-    <t>e_BR51-500,e_BR72-500,e_BR46-500,e_BR105-500,e_BR208-500,e_BR63-500,e_BR80-500,e_BR78-500</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_BR1012-500,e_w526083475-525,e_w526083466-525,e_BR1014-525,e_w526061686-500,e_w526061686-525,e_BR1013-525,e_w466973262-525</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500,e_BR357-500,e_BR367-500,e_BR300-500</t>
-  </si>
-  <si>
-    <t>e_BR838-500,e_BR837-525,e_BR866-500,e_BR837-500,e_BR886-500</t>
-  </si>
-  <si>
-    <t>e_BR435-500,e_BR384-500,e_BR381-500,e_BR367-500,e_BR310-500,e_BR300-500,e_BR433-500,e_BR437-500,e_w953014442-500,e_BR309-500</t>
-  </si>
-  <si>
-    <t>e_BR355-500,e_BR321-500,e_BR293-500,e_BR282-500,e_BR360-500,e_BR323-500,e_BR344-500,e_BR302-500,e_BR340-500,e_w603494578-500</t>
-  </si>
-  <si>
-    <t>e_BR487-500,e_BR609-440,e_BR541-500,e_BR515-500,e_BR544-500,e_w302931307-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>e_BR550-500,e_BR525-500,e_BR490-500,e_BR493-500</t>
-  </si>
-  <si>
-    <t>e_BR319-230,e_BR318-230,e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_BR315-230,e_w201470687-500,e_BR273-230,e_BR270-230,e_BR327-230</t>
-  </si>
-  <si>
-    <t>e_w168904844-230,e_BR411-230,e_w168904844-500</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR626-440,e_w302901044-440,e_BR487-500,e_BR609-440</t>
-  </si>
-  <si>
-    <t>e_w515552863-500,e_w525253078-500,e_BR20-500,e_w215284729-500,e_BR77-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR354-500,e_BR278-500,e_BR246-500,e_BR387-500,e_BR254-500,e_BR413-500,e_BR366-500,e_BR363-500,e_BR339-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR337-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>e_BR274-500,e_w304646981-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500</t>
-  </si>
-  <si>
-    <t>e_BR592-500,e_BR602-500,e_BR556-500,e_BR642-500,e_BR580-500,e_BR596-500,e_BR659-500,e_BR610-500,e_BR583-500</t>
-  </si>
-  <si>
-    <t>e_BR571-500,e_BR528-500,e_BR483-500,e_w954122148-500,e_BR499-500</t>
-  </si>
-  <si>
-    <t>e_w284868411-230,e_BR327-230,e_BR315-230</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_BR657-440</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR369-500</t>
-  </si>
-  <si>
-    <t>e_BR788-500,e_w125761912-500,e_w125761912-765,e_BR732-500,e_w202622375-765,e_BR676-440,e_BR786-500,e_BR781-500</t>
-  </si>
-  <si>
-    <t>e_BR610-500,e_BR605-500,e_BR571-500,e_BR652-500,e_BR643-500,e_BR587-500,e_BR558-500,e_BR627-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>e_BR303-230,e_BR284-500,e_BR274-500</t>
-  </si>
-  <si>
-    <t>e_BR270-230,e_BR283-500</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR876-500</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR446-500,e_BR487-500</t>
-  </si>
-  <si>
-    <t>e_w453724535-500,e_BR369-500,e_BR357-500,e_BR347-500,e_BR446-500</t>
-  </si>
-  <si>
-    <t>e_w525253078-500</t>
-  </si>
-  <si>
-    <t>e_BR446-500,e_BR487-500,e_BR435-500,e_BR367-500,e_w306104018-500</t>
-  </si>
-  <si>
-    <t>e_BR20-500,e_BR15-500,e_BR61-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>e_w287374167-500,e_BR24-500,e_w285044818-500</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440</t>
-  </si>
-  <si>
-    <t>e_BR487-500,e_BR515-500,e_w306104018-500,e_r6844204-500,e_BR490-500</t>
-  </si>
-  <si>
-    <t>e_BR837-500,e_BR837-525,e_BR866-500,e_BR788-500,e_BR845-500,e_w167516187-500,e_BR886-500,e_BR862-500,e_BR849-500</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w626479359-500,e_BR659-500,e_BR689-500,e_BR674-500,e_BR610-500,e_w108224468-500,e_BR683-500,e_BR652-500</t>
-  </si>
-  <si>
     <t>e_w284868411-230,e_BR284-500,e_BR285-500,e_w201470687-230,e_BR274-500</t>
   </si>
   <si>
@@ -2728,6 +2728,54 @@
     <t>e_BR209-500,e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR80-500,e_BR282-500,e_BR148-500,e_BR120-500,e_w603494578-500,e_BR194-500,e_BR187-500,e_BR114-500,e_BR164-500,e_BR142-500</t>
   </si>
   <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_010</t>
   </si>
   <si>
@@ -2752,6 +2800,198 @@
     <t>connecting wind onshore to buses in cluster 63</t>
   </si>
   <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_067</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_031</t>
   </si>
   <si>
@@ -2782,132 +3022,6 @@
     <t>connecting wind onshore to buses in cluster 45</t>
   </si>
   <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_005</t>
   </si>
   <si>
@@ -2926,6 +3040,72 @@
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_068</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_048</t>
   </si>
   <si>
@@ -2962,184 +3142,52 @@
     <t>connecting wind onshore to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_068</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_067</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_BR837-525,e_BR788-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
+  </si>
+  <si>
+    <t>elc_won_055</t>
+  </si>
+  <si>
+    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
+  </si>
+  <si>
+    <t>elc_won_060</t>
+  </si>
+  <si>
+    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
   </si>
   <si>
     <t>elc_won_010</t>
@@ -3166,6 +3214,195 @@
     <t>e_BR473-500,e_BR437-500,e_BR382-500,e_BR373-500,e_BR428-500</t>
   </si>
   <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_won_067</t>
+  </si>
+  <si>
+    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
+  </si>
+  <si>
+    <t>elc_won_058</t>
+  </si>
+  <si>
+    <t>e_BR220-500,e_BR185-500</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
+  </si>
+  <si>
+    <t>elc_won_062</t>
+  </si>
+  <si>
+    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
+  </si>
+  <si>
+    <t>elc_won_047</t>
+  </si>
+  <si>
+    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w188465343-500,e_BR909-500,e_BR858-500,e_w521542011-500</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
+  </si>
+  <si>
+    <t>elc_won_061</t>
+  </si>
+  <si>
+    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_BR412-500,e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
+  </si>
+  <si>
+    <t>elc_won_053</t>
+  </si>
+  <si>
+    <t>e_BR886-500,e_BR862-500</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
+  </si>
+  <si>
+    <t>elc_won_049</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_won_044</t>
+  </si>
+  <si>
+    <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
+  </si>
+  <si>
+    <t>elc_won_046</t>
+  </si>
+  <si>
+    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w168904844-500,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
+  </si>
+  <si>
+    <t>elc_won_059</t>
+  </si>
+  <si>
+    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
+  </si>
+  <si>
+    <t>elc_won_051</t>
+  </si>
+  <si>
+    <t>e_BR613-500,e_BR579-500</t>
+  </si>
+  <si>
     <t>elc_won_031</t>
   </si>
   <si>
@@ -3196,132 +3433,6 @@
     <t>e_BR46-500,e_BR63-500,e_BR78-500,e_BR80-500,e_BR103-500,e_w603494578-500,e_BR114-500,e_BR204-500,e_BR187-500,e_BR164-500,e_BR142-500,e_w532354815-500,e_BR159-500,e_BR135-500,e_w348815398-500,e_BR227-500,e_w1090304792-500,e_BR154-500,e_BR258-500</t>
   </si>
   <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w32300871-525,e_BR803-500,e_BR876-500,e_BR820-500,e_BR787-500,e_BR787-525,e_w188465343-500</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_BR676-440,e_BR676-500,e_BR646-440,e_w174017677-440,e_BR630-440,e_BR663-440,e_BR661-440,e_w302735025-500,e_w302735025-440,e_BR670-440,e_BR650-440,e_BR641-500,e_BR666-440,e_BR686-500</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_BR820-500,e_w150728360-500,e_BR787-525,e_BR858-500,e_w188465343-500,e_BR833-500,e_w521542011-500,e_BR838-500,e_BR837-525,e_BR832-500</t>
-  </si>
-  <si>
-    <t>elc_won_053</t>
-  </si>
-  <si>
-    <t>e_BR886-500,e_BR862-500</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500,e_BR41-500</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_BR464-500,e_w596594961-500,e_BR462-500,e_BR439-500,e_BR413-500,e_BR387-500,e_BR354-500,e_BR363-500,e_BR339-500,e_BR337-500,e_BR308-500</t>
-  </si>
-  <si>
-    <t>elc_won_049</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR499-500,e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_won_044</t>
-  </si>
-  <si>
-    <t>e_BR400-500,e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_w302901044-440,e_BR609-440,e_BR487-500</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w626452961-500,e_w466973262-525,e_w969586211-525,e_w528904118-500,e_BR947-525</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_w168664395-500,e_BR626-440</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_BR909-500,e_BR904-500,e_w247684836-500,e_BR903-500</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_w125761912-500,e_w125761912-765,e_BR732-500,e_BR673-440,e_BR676-440</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_BR837-525,e_BR788-500,e_BR845-500,e_w167516187-500,e_w131742617-500,e_BR802-500,e_BR786-500,e_w202622375-765</t>
-  </si>
-  <si>
-    <t>elc_won_055</t>
-  </si>
-  <si>
-    <t>e_BR384-500,e_w953014442-500,e_BR309-500,e_BR373-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_060</t>
-  </si>
-  <si>
-    <t>e_BR373-500,e_w953014442-500,e_BR309-500,e_BR333-500,e_BR220-500</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_BR876-500,e_BR878-500,e_w188465343-500,e_BR909-500,e_BR858-500,e_w521542011-500</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_BR609-440,e_BR624-440,e_w286006777-440,e_BR632-440,e_w302931307-440,e_BR544-500,e_w302931307-500,e_BR628-440,e_w537470701-500,e_BR606-500</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_BR606-500,e_BR629-500,e_w174852067-440,e_BR592-500,e_BR642-500</t>
-  </si>
-  <si>
-    <t>elc_won_061</t>
-  </si>
-  <si>
-    <t>e_BR333-500,e_BR246-500,e_BR185-500,e_BR354-500,e_BR278-500,e_BR254-500,e_BR308-500,e_BR276-500,e_BR248-500,e_BR221-500,e_BR264-500,e_BR236-500</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_BR412-500,e_BR400-500</t>
-  </si>
-  <si>
     <t>elc_won_005</t>
   </si>
   <si>
@@ -3340,6 +3451,69 @@
     <t>e_BR728-440,e_w225181494-500,e_BR744-440,e_BR746-500,e_BR700-500</t>
   </si>
   <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
+  </si>
+  <si>
+    <t>elc_won_054</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
+  </si>
+  <si>
+    <t>elc_won_043</t>
+  </si>
+  <si>
+    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_BR209-500,e_BR208-500</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
+  </si>
+  <si>
+    <t>elc_won_066</t>
+  </si>
+  <si>
+    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
+  </si>
+  <si>
+    <t>elc_won_068</t>
+  </si>
+  <si>
+    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
+  </si>
+  <si>
     <t>elc_won_048</t>
   </si>
   <si>
@@ -3373,178 +3547,94 @@
     <t>e_BR400-500,e_BR360-500,e_BR355-500,e_BR321-500,e_BR323-500,e_BR293-500,e_BR344-500,e_BR302-500,e_BR340-500</t>
   </si>
   <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w168904844-500,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w202622375-765,e_BR676-440,e_BR781-500,e_BR663-440,e_BR728-440,e_BR670-440,e_w172071437-440,e_BR696-500</t>
-  </si>
-  <si>
-    <t>elc_won_059</t>
-  </si>
-  <si>
-    <t>e_BR309-500,e_BR220-500,e_BR185-500,e_BR122-500</t>
-  </si>
-  <si>
-    <t>elc_won_051</t>
-  </si>
-  <si>
-    <t>e_BR613-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_r9328495-500,e_w626452961-500,e_BR878-500,e_BR1012-500,e_w526061686-525</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_BR626-440,e_BR609-440,e_w302901044-440,e_BR541-500</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>e_BR662-440,e_BR639-440,e_BR673-440,e_BR676-500,e_BR632-440,e_w174017677-440</t>
-  </si>
-  <si>
-    <t>elc_won_062</t>
-  </si>
-  <si>
-    <t>e_BR506-500,e_BR473-500,e_BR483-500,e_BR478-500,e_BR437-500</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_BR528-500,e_BR499-500,e_w954122148-500,e_BR462-500,e_BR439-500,e_BR535-500,e_BR459-500,e_BR430-500,e_BR413-500</t>
-  </si>
-  <si>
-    <t>elc_won_047</t>
-  </si>
-  <si>
-    <t>e_BR122-500,e_BR72-500,e_BR221-500,e_BR105-500,e_BR46-500,e_BR63-500,e_BR80-500</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_BR777-500,e_w168904844-230,e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_066</t>
-  </si>
-  <si>
-    <t>e_BR515-500,e_w306104018-500,e_BR544-500</t>
-  </si>
-  <si>
-    <t>elc_won_068</t>
-  </si>
-  <si>
-    <t>e_r6844204-500,e_w306104018-500,e_BR490-500,e_BR482-500</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_BR366-500,e_BR363-500,e_BR343-500,e_BR337-500,e_BR308-500,e_BR294-500,e_BR304-500,e_BR296-500,e_BR236-500,e_BR321-500,e_BR282-500,e_BR209-500,e_BR293-500,e_w603494578-500,e_BR194-500</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w168664395-500</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_BR541-500,e_w302931307-500,e_BR544-500,e_w537470701-500,e_r6844204-500</t>
-  </si>
-  <si>
-    <t>elc_won_054</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_w539025237-440,e_BR689-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_BR596-500,e_BR659-500,e_BR610-500</t>
-  </si>
-  <si>
-    <t>elc_won_043</t>
-  </si>
-  <si>
-    <t>e_BR61-500,e_BR37-500,e_BR41-500,e_BR49-500,e_BR42-500,e_BR51-500</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_BR209-500,e_BR208-500</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_w168664395-500,e_BR487-500,e_BR515-500</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_BR657-440,e_BR626-440,e_BR662-440,e_w302901044-440</t>
-  </si>
-  <si>
-    <t>elc_won_064</t>
-  </si>
-  <si>
-    <t>e_BR578-500,e_BR528-500,e_BR506-500,e_BR483-500,e_BR478-500,e_w954122148-500,e_BR464-500,e_BR462-500</t>
-  </si>
-  <si>
-    <t>elc_won_046</t>
-  </si>
-  <si>
-    <t>e_BR208-500,e_BR105-500,e_BR190-500,e_BR103-500,e_BR148-500,e_BR120-500,e_BR194-500,e_BR187-500</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_w285044818-500,e_w525253078-500,e_BR20-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_won_067</t>
-  </si>
-  <si>
-    <t>e_w537470701-500,e_BR550-500,e_BR525-500,e_BR592-500,e_w174852067-500,e_BR602-500,e_BR642-500,e_BR556-500</t>
-  </si>
-  <si>
-    <t>elc_won_058</t>
-  </si>
-  <si>
-    <t>e_BR220-500,e_BR185-500</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_BR430-500,e_BR459-500,e_BR366-500,e_BR412-500,e_BR363-500,e_BR337-500,e_BR355-500,e_BR321-500</t>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_026</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_030</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_001</t>
@@ -3565,6 +3655,54 @@
     <t>connecting wind offshore to buses in cluster 31</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_012</t>
   </si>
   <si>
@@ -3577,64 +3715,10 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_026</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_030</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 30</t>
+    <t>distr_wofelc_wof_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
   </si>
   <si>
     <t>distr_wofelc_wof_025</t>
@@ -3649,88 +3733,91 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_BR459-500</t>
+  </si>
+  <si>
+    <t>elc_wof_026</t>
+  </si>
+  <si>
+    <t>e_BR400-500</t>
+  </si>
+  <si>
+    <t>elc_wof_030</t>
+  </si>
+  <si>
+    <t>e_BR154-500</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_BR851-500,e_w385000005-500</t>
+  </si>
+  <si>
+    <t>elc_wof_024</t>
+  </si>
+  <si>
+    <t>e_BR15-500,e_BR37-500</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_BR691-500,e_w108224468-500</t>
+  </si>
+  <si>
+    <t>elc_wof_028</t>
+  </si>
+  <si>
+    <t>e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
+  </si>
+  <si>
+    <t>elc_wof_029</t>
+  </si>
+  <si>
+    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
+  </si>
+  <si>
+    <t>elc_wof_023</t>
+  </si>
+  <si>
+    <t>e_BR652-500,e_BR644-500</t>
+  </si>
+  <si>
+    <t>elc_wof_021</t>
+  </si>
+  <si>
+    <t>e_BR579-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
   </si>
   <si>
     <t>elc_wof_001</t>
@@ -3751,6 +3838,48 @@
     <t>e_BR78-500,e_BR80-500,e_BR114-500,e_BR103-500,e_BR135-500,e_BR154-500</t>
   </si>
   <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
+  </si>
+  <si>
+    <t>elc_wof_022</t>
+  </si>
+  <si>
+    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_BR992-525,e_BR886-500</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w525253078-500,e_BR15-500</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
     <t>elc_wof_012</t>
   </si>
   <si>
@@ -3763,61 +3892,10 @@
     <t>e_w108224468-500,e_BR652-500</t>
   </si>
   <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_BR499-500,e_BR459-500,e_BR579-500</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_BR992-525,e_BR886-500</t>
-  </si>
-  <si>
-    <t>elc_wof_021</t>
-  </si>
-  <si>
-    <t>e_BR579-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w525253078-500,e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_BR862-500,e_BR851-500,e_BR764-440,e_BR758-440</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_BR459-500</t>
-  </si>
-  <si>
-    <t>elc_wof_026</t>
-  </si>
-  <si>
-    <t>e_BR400-500</t>
-  </si>
-  <si>
-    <t>elc_wof_030</t>
-  </si>
-  <si>
-    <t>e_BR154-500</t>
+    <t>elc_wof_027</t>
+  </si>
+  <si>
+    <t>e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
   </si>
   <si>
     <t>elc_wof_025</t>
@@ -3830,84 +3908,6 @@
   </si>
   <si>
     <t>e_w466973262-525,e_BR992-525</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_BR15-500</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_BR851-500,e_w385000005-500</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w526083475-525,e_w526083466-525,e_BR1014-525</t>
-  </si>
-  <si>
-    <t>elc_wof_029</t>
-  </si>
-  <si>
-    <t>e_BR42-500,e_BR51-500,e_BR46-500,e_BR63-500</t>
-  </si>
-  <si>
-    <t>elc_wof_023</t>
-  </si>
-  <si>
-    <t>e_BR652-500,e_BR644-500</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_BR758-440,e_BR755-500,e_BR713-500,e_w287393618-500,e_BR691-500</t>
-  </si>
-  <si>
-    <t>elc_wof_022</t>
-  </si>
-  <si>
-    <t>e_BR644-500,e_BR627-500,e_BR613-500</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>elc_wof_024</t>
-  </si>
-  <si>
-    <t>e_BR15-500,e_BR37-500</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_BR691-500,e_w108224468-500</t>
-  </si>
-  <si>
-    <t>elc_wof_028</t>
-  </si>
-  <si>
-    <t>e_w1090304792-500,e_BR154-500,e_BR258-500,e_w348815398-500</t>
-  </si>
-  <si>
-    <t>elc_wof_027</t>
-  </si>
-  <si>
-    <t>e_BR344-500,e_BR340-500,e_BR292-500,e_BR258-500</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -9678,7 +9678,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D94409ED-B123-4849-B4B9-FA124303D69C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{152C235F-FB01-4B83-BCA1-84E25C84FCED}">
   <dimension ref="B9:BD125"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9916,16 +9916,16 @@
         <v>525</v>
       </c>
       <c r="Y11" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="Z11" t="s">
         <v>759</v>
       </c>
       <c r="AA11">
-        <v>0.96988338866662871</v>
+        <v>0.96520767961718001</v>
       </c>
       <c r="AB11">
-        <v>552.13787444514003</v>
+        <v>637.85920701836687</v>
       </c>
       <c r="AD11" t="s">
         <v>524</v>
@@ -9958,10 +9958,10 @@
         <v>1005</v>
       </c>
       <c r="AO11">
-        <v>0.99424679200457</v>
+        <v>0.99551365545858539</v>
       </c>
       <c r="AP11">
-        <v>105.47547991621673</v>
+        <v>82.249649925934918</v>
       </c>
       <c r="AR11" t="s">
         <v>524</v>
@@ -9994,10 +9994,10 @@
         <v>1202</v>
       </c>
       <c r="BC11">
-        <v>0.98890025255868685</v>
+        <v>0.99054926914187857</v>
       </c>
       <c r="BD11">
-        <v>203.49536975740753</v>
+        <v>173.26339906555947</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -10062,16 +10062,16 @@
         <v>529</v>
       </c>
       <c r="Y12" t="s">
-        <v>488</v>
+        <v>412</v>
       </c>
       <c r="Z12" t="s">
         <v>760</v>
       </c>
       <c r="AA12">
-        <v>0.99464376574467439</v>
+        <v>0.98762421667584677</v>
       </c>
       <c r="AB12">
-        <v>98.197628014302481</v>
+        <v>226.88936094280919</v>
       </c>
       <c r="AD12" t="s">
         <v>524</v>
@@ -10104,10 +10104,10 @@
         <v>1007</v>
       </c>
       <c r="AO12">
-        <v>0.99762284649610655</v>
+        <v>0.9972012891192491</v>
       </c>
       <c r="AP12">
-        <v>43.581147571379539</v>
+        <v>51.309699480432613</v>
       </c>
       <c r="AR12" t="s">
         <v>524</v>
@@ -10140,10 +10140,10 @@
         <v>1204</v>
       </c>
       <c r="BC12">
-        <v>0.99481196273061234</v>
+        <v>0.98163861082146986</v>
       </c>
       <c r="BD12">
-        <v>95.114016605440895</v>
+        <v>336.62546827305243</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -10208,16 +10208,16 @@
         <v>531</v>
       </c>
       <c r="Y13" t="s">
-        <v>491</v>
+        <v>436</v>
       </c>
       <c r="Z13" t="s">
         <v>761</v>
       </c>
       <c r="AA13">
-        <v>0.98289281118622185</v>
+        <v>0.99519314522306834</v>
       </c>
       <c r="AB13">
-        <v>313.63179491926536</v>
+        <v>88.125670910414172</v>
       </c>
       <c r="AD13" t="s">
         <v>524</v>
@@ -10250,10 +10250,10 @@
         <v>1009</v>
       </c>
       <c r="AO13">
-        <v>0.99648541839873139</v>
+        <v>0.97651207122624506</v>
       </c>
       <c r="AP13">
-        <v>64.433996023258757</v>
+        <v>430.61202751883985</v>
       </c>
       <c r="AR13" t="s">
         <v>524</v>
@@ -10286,10 +10286,10 @@
         <v>1206</v>
       </c>
       <c r="BC13">
-        <v>0.99374755699184159</v>
+        <v>0.99665799830099</v>
       </c>
       <c r="BD13">
-        <v>114.62812181623703</v>
+        <v>61.270031148516708</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -10354,16 +10354,16 @@
         <v>533</v>
       </c>
       <c r="Y14" t="s">
-        <v>480</v>
+        <v>444</v>
       </c>
       <c r="Z14" t="s">
         <v>762</v>
       </c>
       <c r="AA14">
-        <v>0.99395687253312803</v>
+        <v>0.99377714174527498</v>
       </c>
       <c r="AB14">
-        <v>110.79067022598578</v>
+        <v>114.08573466995766</v>
       </c>
       <c r="AD14" t="s">
         <v>524</v>
@@ -10396,10 +10396,10 @@
         <v>1011</v>
       </c>
       <c r="AO14">
-        <v>0.99445933293330402</v>
+        <v>0.99567626923235475</v>
       </c>
       <c r="AP14">
-        <v>101.57889622275951</v>
+        <v>79.268397406829976</v>
       </c>
       <c r="AR14" t="s">
         <v>524</v>
@@ -10432,10 +10432,10 @@
         <v>1208</v>
       </c>
       <c r="BC14">
-        <v>0.98946506962487613</v>
+        <v>0.98125520899414764</v>
       </c>
       <c r="BD14">
-        <v>193.14039021060518</v>
+        <v>343.65450177395917</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -10500,16 +10500,16 @@
         <v>535</v>
       </c>
       <c r="Y15" t="s">
-        <v>438</v>
+        <v>510</v>
       </c>
       <c r="Z15" t="s">
         <v>763</v>
       </c>
       <c r="AA15">
-        <v>0.99480158385008166</v>
+        <v>0.99008735429887684</v>
       </c>
       <c r="AB15">
-        <v>95.304296081836526</v>
+        <v>181.7318378539255</v>
       </c>
       <c r="AD15" t="s">
         <v>524</v>
@@ -10542,10 +10542,10 @@
         <v>1013</v>
       </c>
       <c r="AO15">
-        <v>0.99620534810300254</v>
+        <v>0.9974675531234084</v>
       </c>
       <c r="AP15">
-        <v>69.568618111619969</v>
+        <v>46.428192737512276</v>
       </c>
       <c r="AR15" t="s">
         <v>524</v>
@@ -10578,10 +10578,10 @@
         <v>1210</v>
       </c>
       <c r="BC15">
-        <v>0.99314574070258299</v>
+        <v>0.96863461872110523</v>
       </c>
       <c r="BD15">
-        <v>125.66142045264445</v>
+        <v>575.0319901130714</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -10646,16 +10646,16 @@
         <v>537</v>
       </c>
       <c r="Y16" t="s">
-        <v>457</v>
+        <v>427</v>
       </c>
       <c r="Z16" t="s">
         <v>764</v>
       </c>
       <c r="AA16">
-        <v>0.99338478208530079</v>
+        <v>0.99219431421335524</v>
       </c>
       <c r="AB16">
-        <v>121.27899510281891</v>
+        <v>143.10423942182081</v>
       </c>
       <c r="AD16" t="s">
         <v>524</v>
@@ -10688,10 +10688,10 @@
         <v>1015</v>
       </c>
       <c r="AO16">
-        <v>0.9961850470371636</v>
+        <v>0.99694661611560498</v>
       </c>
       <c r="AP16">
-        <v>69.94080431866837</v>
+        <v>55.978704547242401</v>
       </c>
       <c r="AR16" t="s">
         <v>524</v>
@@ -10721,13 +10721,13 @@
         <v>1211</v>
       </c>
       <c r="BB16" t="s">
-        <v>1212</v>
+        <v>1066</v>
       </c>
       <c r="BC16">
-        <v>0.97821242976023937</v>
+        <v>0.99098965084511315</v>
       </c>
       <c r="BD16">
-        <v>399.43878772894504</v>
+        <v>165.18973450625904</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -10792,16 +10792,16 @@
         <v>539</v>
       </c>
       <c r="Y17" t="s">
-        <v>519</v>
+        <v>489</v>
       </c>
       <c r="Z17" t="s">
         <v>765</v>
       </c>
       <c r="AA17">
-        <v>0.99506672623055659</v>
+        <v>0.99107116626800151</v>
       </c>
       <c r="AB17">
-        <v>90.443352439796072</v>
+        <v>163.69528508663959</v>
       </c>
       <c r="AD17" t="s">
         <v>524</v>
@@ -10834,10 +10834,10 @@
         <v>1017</v>
       </c>
       <c r="AO17">
-        <v>0.99681385284485569</v>
+        <v>0.99175391794306234</v>
       </c>
       <c r="AP17">
-        <v>58.41269784431158</v>
+        <v>151.17817104385733</v>
       </c>
       <c r="AR17" t="s">
         <v>524</v>
@@ -10864,16 +10864,16 @@
         <v>1151</v>
       </c>
       <c r="BA17" t="s">
+        <v>1212</v>
+      </c>
+      <c r="BB17" t="s">
         <v>1213</v>
       </c>
-      <c r="BB17" t="s">
-        <v>1214</v>
-      </c>
       <c r="BC17">
-        <v>0.99203097418485064</v>
+        <v>0.99053278045305837</v>
       </c>
       <c r="BD17">
-        <v>146.09880661107059</v>
+        <v>173.56569169392964</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -10938,16 +10938,16 @@
         <v>541</v>
       </c>
       <c r="Y18" t="s">
-        <v>509</v>
+        <v>415</v>
       </c>
       <c r="Z18" t="s">
         <v>766</v>
       </c>
       <c r="AA18">
-        <v>0.98810060695535451</v>
+        <v>0.99653079856255411</v>
       </c>
       <c r="AB18">
-        <v>218.15553915183366</v>
+        <v>63.602026353175077</v>
       </c>
       <c r="AD18" t="s">
         <v>524</v>
@@ -10980,10 +10980,10 @@
         <v>1019</v>
       </c>
       <c r="AO18">
-        <v>0.99274560110857168</v>
+        <v>0.99414234808301016</v>
       </c>
       <c r="AP18">
-        <v>132.99731300951822</v>
+        <v>107.39028514481463</v>
       </c>
       <c r="AR18" t="s">
         <v>524</v>
@@ -11010,16 +11010,16 @@
         <v>1153</v>
       </c>
       <c r="BA18" t="s">
+        <v>1214</v>
+      </c>
+      <c r="BB18" t="s">
         <v>1215</v>
       </c>
-      <c r="BB18" t="s">
-        <v>1216</v>
-      </c>
       <c r="BC18">
-        <v>0.98574436213546524</v>
+        <v>0.98027195861782945</v>
       </c>
       <c r="BD18">
-        <v>261.35336084980423</v>
+        <v>361.68075867312689</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -11084,16 +11084,16 @@
         <v>543</v>
       </c>
       <c r="Y19" t="s">
-        <v>507</v>
+        <v>433</v>
       </c>
       <c r="Z19" t="s">
         <v>767</v>
       </c>
       <c r="AA19">
-        <v>0.98820036495460695</v>
+        <v>0.99516969310216208</v>
       </c>
       <c r="AB19">
-        <v>216.32664249887239</v>
+        <v>88.555626460362205</v>
       </c>
       <c r="AD19" t="s">
         <v>524</v>
@@ -11126,10 +11126,10 @@
         <v>1021</v>
       </c>
       <c r="AO19">
-        <v>0.99746043308117838</v>
+        <v>0.99424679200457</v>
       </c>
       <c r="AP19">
-        <v>46.558726845063177</v>
+        <v>105.47547991621673</v>
       </c>
       <c r="AR19" t="s">
         <v>524</v>
@@ -11156,16 +11156,16 @@
         <v>1155</v>
       </c>
       <c r="BA19" t="s">
+        <v>1216</v>
+      </c>
+      <c r="BB19" t="s">
         <v>1217</v>
       </c>
-      <c r="BB19" t="s">
-        <v>1218</v>
-      </c>
       <c r="BC19">
-        <v>0.95713629889852414</v>
+        <v>0.9959052853503485</v>
       </c>
       <c r="BD19">
-        <v>785.83452019372396</v>
+        <v>75.06976857694373</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -11230,16 +11230,16 @@
         <v>545</v>
       </c>
       <c r="Y20" t="s">
-        <v>505</v>
+        <v>470</v>
       </c>
       <c r="Z20" t="s">
         <v>768</v>
       </c>
       <c r="AA20">
-        <v>0.97404342257401955</v>
+        <v>0.98827949012946181</v>
       </c>
       <c r="AB20">
-        <v>475.8705861429753</v>
+        <v>214.8760142931996</v>
       </c>
       <c r="AD20" t="s">
         <v>524</v>
@@ -11272,10 +11272,10 @@
         <v>1023</v>
       </c>
       <c r="AO20">
-        <v>0.99551365545858539</v>
+        <v>0.99762284649610655</v>
       </c>
       <c r="AP20">
-        <v>82.249649925934918</v>
+        <v>43.581147571379539</v>
       </c>
       <c r="AR20" t="s">
         <v>524</v>
@@ -11302,16 +11302,16 @@
         <v>1157</v>
       </c>
       <c r="BA20" t="s">
+        <v>1218</v>
+      </c>
+      <c r="BB20" t="s">
         <v>1219</v>
       </c>
-      <c r="BB20" t="s">
-        <v>1214</v>
-      </c>
       <c r="BC20">
-        <v>0.98806872821788805</v>
+        <v>0.99538398111052984</v>
       </c>
       <c r="BD20">
-        <v>218.73998267205184</v>
+        <v>84.627012973619784</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -11376,16 +11376,16 @@
         <v>547</v>
       </c>
       <c r="Y21" t="s">
-        <v>475</v>
+        <v>422</v>
       </c>
       <c r="Z21" t="s">
         <v>769</v>
       </c>
       <c r="AA21">
-        <v>0.99284309609540211</v>
+        <v>0.99780983219878738</v>
       </c>
       <c r="AB21">
-        <v>131.20990491762768</v>
+        <v>40.153076355563911</v>
       </c>
       <c r="AD21" t="s">
         <v>524</v>
@@ -11418,10 +11418,10 @@
         <v>1025</v>
       </c>
       <c r="AO21">
-        <v>0.9972012891192491</v>
+        <v>0.99648541839873139</v>
       </c>
       <c r="AP21">
-        <v>51.309699480432613</v>
+        <v>64.433996023258757</v>
       </c>
       <c r="AR21" t="s">
         <v>524</v>
@@ -11454,10 +11454,10 @@
         <v>1221</v>
       </c>
       <c r="BC21">
-        <v>0.98691003029105739</v>
+        <v>0.99834679070917032</v>
       </c>
       <c r="BD21">
-        <v>239.98277799728109</v>
+        <v>30.308836998544216</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -11522,16 +11522,16 @@
         <v>549</v>
       </c>
       <c r="Y22" t="s">
-        <v>481</v>
+        <v>437</v>
       </c>
       <c r="Z22" t="s">
         <v>770</v>
       </c>
       <c r="AA22">
-        <v>0.99247189917622181</v>
+        <v>0.99478593896263345</v>
       </c>
       <c r="AB22">
-        <v>138.01518176926754</v>
+        <v>95.59111901838736</v>
       </c>
       <c r="AD22" t="s">
         <v>524</v>
@@ -11564,10 +11564,10 @@
         <v>1027</v>
       </c>
       <c r="AO22">
-        <v>0.99684152237002188</v>
+        <v>0.99445933293330402</v>
       </c>
       <c r="AP22">
-        <v>57.905423216266421</v>
+        <v>101.57889622275951</v>
       </c>
       <c r="AR22" t="s">
         <v>524</v>
@@ -11600,10 +11600,10 @@
         <v>1223</v>
       </c>
       <c r="BC22">
-        <v>0.99054926914187857</v>
+        <v>0.99401640271965719</v>
       </c>
       <c r="BD22">
-        <v>173.26339906555947</v>
+        <v>109.69928347295183</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -11668,16 +11668,16 @@
         <v>551</v>
       </c>
       <c r="Y23" t="s">
-        <v>487</v>
+        <v>466</v>
       </c>
       <c r="Z23" t="s">
         <v>771</v>
       </c>
       <c r="AA23">
-        <v>0.98563153879963317</v>
+        <v>0.99431447054153432</v>
       </c>
       <c r="AB23">
-        <v>263.42178867339101</v>
+        <v>104.23470673853728</v>
       </c>
       <c r="AD23" t="s">
         <v>524</v>
@@ -11710,10 +11710,10 @@
         <v>1029</v>
       </c>
       <c r="AO23">
-        <v>0.99679967385551038</v>
+        <v>0.98589595763902149</v>
       </c>
       <c r="AP23">
-        <v>58.672645982308907</v>
+        <v>258.57410995127316</v>
       </c>
       <c r="AR23" t="s">
         <v>524</v>
@@ -11746,10 +11746,10 @@
         <v>1225</v>
       </c>
       <c r="BC23">
-        <v>0.98163861082146986</v>
+        <v>0.9933934749176847</v>
       </c>
       <c r="BD23">
-        <v>336.62546827305243</v>
+        <v>121.11962650911367</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -11814,16 +11814,16 @@
         <v>553</v>
       </c>
       <c r="Y24" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="Z24" t="s">
         <v>772</v>
       </c>
       <c r="AA24">
-        <v>0.99704166323096854</v>
+        <v>0.99649132983250632</v>
       </c>
       <c r="AB24">
-        <v>54.23617409891024</v>
+        <v>64.325619737385011</v>
       </c>
       <c r="AD24" t="s">
         <v>524</v>
@@ -11856,10 +11856,10 @@
         <v>1031</v>
       </c>
       <c r="AO24">
-        <v>0.99083036293819104</v>
+        <v>0.99554924619735208</v>
       </c>
       <c r="AP24">
-        <v>168.11001279983091</v>
+        <v>81.597153048545437</v>
       </c>
       <c r="AR24" t="s">
         <v>524</v>
@@ -11892,10 +11892,10 @@
         <v>1227</v>
       </c>
       <c r="BC24">
-        <v>0.99665799830099</v>
+        <v>0.98574436213546524</v>
       </c>
       <c r="BD24">
-        <v>61.270031148516708</v>
+        <v>261.35336084980423</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -11960,16 +11960,16 @@
         <v>555</v>
       </c>
       <c r="Y25" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="Z25" t="s">
         <v>773</v>
       </c>
       <c r="AA25">
-        <v>0.99529226044395613</v>
+        <v>0.9925766880786181</v>
       </c>
       <c r="AB25">
-        <v>86.308558527470979</v>
+        <v>136.09405189200152</v>
       </c>
       <c r="AD25" t="s">
         <v>524</v>
@@ -12002,10 +12002,10 @@
         <v>1033</v>
       </c>
       <c r="AO25">
-        <v>0.99710531380540124</v>
+        <v>0.99534886842510228</v>
       </c>
       <c r="AP25">
-        <v>53.069246900976879</v>
+        <v>85.270745539791065</v>
       </c>
       <c r="AR25" t="s">
         <v>524</v>
@@ -12038,10 +12038,10 @@
         <v>1229</v>
       </c>
       <c r="BC25">
-        <v>0.98125520899414764</v>
+        <v>0.98691003029105739</v>
       </c>
       <c r="BD25">
-        <v>343.65450177395917</v>
+        <v>239.98277799728109</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -12106,16 +12106,16 @@
         <v>557</v>
       </c>
       <c r="Y26" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="Z26" t="s">
         <v>774</v>
       </c>
       <c r="AA26">
-        <v>0.99324569511004301</v>
+        <v>0.99638451167998066</v>
       </c>
       <c r="AB26">
-        <v>123.82892298254488</v>
+        <v>66.283952533688392</v>
       </c>
       <c r="AD26" t="s">
         <v>524</v>
@@ -12148,10 +12148,10 @@
         <v>1035</v>
       </c>
       <c r="AO26">
-        <v>0.98829989485605374</v>
+        <v>0.99488275259079373</v>
       </c>
       <c r="AP26">
-        <v>214.50192763901472</v>
+        <v>93.81620250211445</v>
       </c>
       <c r="AR26" t="s">
         <v>524</v>
@@ -12184,10 +12184,10 @@
         <v>1231</v>
       </c>
       <c r="BC26">
-        <v>0.98488330873784669</v>
+        <v>0.98890025255868685</v>
       </c>
       <c r="BD26">
-        <v>277.13933980614473</v>
+        <v>203.49536975740753</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -12252,16 +12252,16 @@
         <v>559</v>
       </c>
       <c r="Y27" t="s">
-        <v>424</v>
+        <v>464</v>
       </c>
       <c r="Z27" t="s">
         <v>775</v>
       </c>
       <c r="AA27">
-        <v>0.99731037386855248</v>
+        <v>0.99306919419080486</v>
       </c>
       <c r="AB27">
-        <v>49.309812409870183</v>
+        <v>127.06477316857749</v>
       </c>
       <c r="AD27" t="s">
         <v>524</v>
@@ -12294,10 +12294,10 @@
         <v>1037</v>
       </c>
       <c r="AO27">
-        <v>0.99663220850609069</v>
+        <v>0.98996241922424166</v>
       </c>
       <c r="AP27">
-        <v>61.742844055003644</v>
+        <v>184.02231422223667</v>
       </c>
       <c r="AR27" t="s">
         <v>524</v>
@@ -12330,10 +12330,10 @@
         <v>1233</v>
       </c>
       <c r="BC27">
-        <v>0.99032129621526932</v>
+        <v>0.99481196273061234</v>
       </c>
       <c r="BD27">
-        <v>177.44290272006148</v>
+        <v>95.114016605440895</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -12398,16 +12398,16 @@
         <v>561</v>
       </c>
       <c r="Y28" t="s">
-        <v>458</v>
+        <v>517</v>
       </c>
       <c r="Z28" t="s">
         <v>776</v>
       </c>
       <c r="AA28">
-        <v>0.99465722366873854</v>
+        <v>0.96988338866662871</v>
       </c>
       <c r="AB28">
-        <v>97.950899406460266</v>
+        <v>552.13787444514003</v>
       </c>
       <c r="AD28" t="s">
         <v>524</v>
@@ -12437,13 +12437,13 @@
         <v>1038</v>
       </c>
       <c r="AN28" t="s">
-        <v>1039</v>
+        <v>830</v>
       </c>
       <c r="AO28">
-        <v>0.98452519237182756</v>
+        <v>0.97416725971121887</v>
       </c>
       <c r="AP28">
-        <v>283.70480651649393</v>
+        <v>473.60023862765331</v>
       </c>
       <c r="AR28" t="s">
         <v>524</v>
@@ -12476,10 +12476,10 @@
         <v>1235</v>
       </c>
       <c r="BC28">
-        <v>0.96863461872110523</v>
+        <v>0.99374755699184159</v>
       </c>
       <c r="BD28">
-        <v>575.0319901130714</v>
+        <v>114.62812181623703</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -12544,16 +12544,16 @@
         <v>563</v>
       </c>
       <c r="Y29" t="s">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="Z29" t="s">
         <v>777</v>
       </c>
       <c r="AA29">
-        <v>0.99703280926921656</v>
+        <v>0.99464376574467439</v>
       </c>
       <c r="AB29">
-        <v>54.398496731030697</v>
+        <v>98.197628014302481</v>
       </c>
       <c r="AD29" t="s">
         <v>524</v>
@@ -12580,16 +12580,16 @@
         <v>902</v>
       </c>
       <c r="AM29" t="s">
+        <v>1039</v>
+      </c>
+      <c r="AN29" t="s">
         <v>1040</v>
       </c>
-      <c r="AN29" t="s">
-        <v>1041</v>
-      </c>
       <c r="AO29">
-        <v>0.99403730604060547</v>
+        <v>0.99105808324017197</v>
       </c>
       <c r="AP29">
-        <v>109.31605592223302</v>
+        <v>163.93514059684662</v>
       </c>
       <c r="AR29" t="s">
         <v>524</v>
@@ -12619,13 +12619,13 @@
         <v>1236</v>
       </c>
       <c r="BB29" t="s">
-        <v>1029</v>
+        <v>1237</v>
       </c>
       <c r="BC29">
-        <v>0.99098965084511315</v>
+        <v>0.99232494426983575</v>
       </c>
       <c r="BD29">
-        <v>165.18973450625904</v>
+        <v>140.70935505301131</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -12690,16 +12690,16 @@
         <v>565</v>
       </c>
       <c r="Y30" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="Z30" t="s">
         <v>778</v>
       </c>
       <c r="AA30">
-        <v>0.93980266520001188</v>
+        <v>0.98289281118622185</v>
       </c>
       <c r="AB30">
-        <v>1103.617804666449</v>
+        <v>313.63179491926536</v>
       </c>
       <c r="AD30" t="s">
         <v>524</v>
@@ -12726,16 +12726,16 @@
         <v>904</v>
       </c>
       <c r="AM30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="AN30" t="s">
         <v>1042</v>
       </c>
-      <c r="AN30" t="s">
-        <v>1043</v>
-      </c>
       <c r="AO30">
-        <v>0.97651207122624506</v>
+        <v>0.99776894175014486</v>
       </c>
       <c r="AP30">
-        <v>430.61202751883985</v>
+        <v>40.90273458067751</v>
       </c>
       <c r="AR30" t="s">
         <v>524</v>
@@ -12762,16 +12762,16 @@
         <v>1177</v>
       </c>
       <c r="BA30" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="BB30" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="BC30">
-        <v>0.99053278045305837</v>
+        <v>0.98775115723917273</v>
       </c>
       <c r="BD30">
-        <v>173.56569169392964</v>
+        <v>224.56211728183334</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -12836,16 +12836,16 @@
         <v>567</v>
       </c>
       <c r="Y31" t="s">
-        <v>512</v>
+        <v>480</v>
       </c>
       <c r="Z31" t="s">
         <v>779</v>
       </c>
       <c r="AA31">
-        <v>0.99645756936252694</v>
+        <v>0.99395687253312803</v>
       </c>
       <c r="AB31">
-        <v>64.944561687006995</v>
+        <v>110.79067022598578</v>
       </c>
       <c r="AD31" t="s">
         <v>524</v>
@@ -12872,16 +12872,16 @@
         <v>906</v>
       </c>
       <c r="AM31" t="s">
+        <v>1043</v>
+      </c>
+      <c r="AN31" t="s">
         <v>1044</v>
       </c>
-      <c r="AN31" t="s">
-        <v>1045</v>
-      </c>
       <c r="AO31">
-        <v>0.99567626923235475</v>
+        <v>0.99336049451151065</v>
       </c>
       <c r="AP31">
-        <v>79.268397406829976</v>
+        <v>121.72426728897108</v>
       </c>
       <c r="AR31" t="s">
         <v>524</v>
@@ -12908,16 +12908,16 @@
         <v>1179</v>
       </c>
       <c r="BA31" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="BB31" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="BC31">
-        <v>0.99834679070917032</v>
+        <v>0.99420451954813838</v>
       </c>
       <c r="BD31">
-        <v>30.308836998544216</v>
+        <v>106.25047495079694</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -12982,16 +12982,16 @@
         <v>569</v>
       </c>
       <c r="Y32" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="Z32" t="s">
         <v>780</v>
       </c>
       <c r="AA32">
-        <v>0.99758516433905853</v>
+        <v>0.99480158385008166</v>
       </c>
       <c r="AB32">
-        <v>44.271987117260508</v>
+        <v>95.304296081836526</v>
       </c>
       <c r="AD32" t="s">
         <v>524</v>
@@ -13018,16 +13018,16 @@
         <v>908</v>
       </c>
       <c r="AM32" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AN32" t="s">
         <v>1046</v>
       </c>
-      <c r="AN32" t="s">
-        <v>1047</v>
-      </c>
       <c r="AO32">
-        <v>0.9974675531234084</v>
+        <v>0.99527237968252791</v>
       </c>
       <c r="AP32">
-        <v>46.428192737512276</v>
+        <v>86.673039153654699</v>
       </c>
       <c r="AR32" t="s">
         <v>524</v>
@@ -13054,16 +13054,16 @@
         <v>1181</v>
       </c>
       <c r="BA32" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="BB32" t="s">
-        <v>1242</v>
+        <v>1090</v>
       </c>
       <c r="BC32">
-        <v>0.99401640271965719</v>
+        <v>0.99418931598784899</v>
       </c>
       <c r="BD32">
-        <v>109.69928347295183</v>
+        <v>106.52920688943452</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -13128,16 +13128,16 @@
         <v>571</v>
       </c>
       <c r="Y33" t="s">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="Z33" t="s">
         <v>781</v>
       </c>
       <c r="AA33">
-        <v>0.99267004448650609</v>
+        <v>0.99338478208530079</v>
       </c>
       <c r="AB33">
-        <v>134.38251774738842</v>
+        <v>121.27899510281891</v>
       </c>
       <c r="AD33" t="s">
         <v>524</v>
@@ -13164,16 +13164,16 @@
         <v>910</v>
       </c>
       <c r="AM33" t="s">
+        <v>1047</v>
+      </c>
+      <c r="AN33" t="s">
         <v>1048</v>
       </c>
-      <c r="AN33" t="s">
-        <v>1049</v>
-      </c>
       <c r="AO33">
-        <v>0.99694661611560498</v>
+        <v>0.9917253583369573</v>
       </c>
       <c r="AP33">
-        <v>55.978704547242401</v>
+        <v>151.70176382244892</v>
       </c>
       <c r="AR33" t="s">
         <v>524</v>
@@ -13206,10 +13206,10 @@
         <v>1244</v>
       </c>
       <c r="BC33">
-        <v>0.9933934749176847</v>
+        <v>0.97821242976023937</v>
       </c>
       <c r="BD33">
-        <v>121.11962650911367</v>
+        <v>399.43878772894504</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -13274,16 +13274,16 @@
         <v>573</v>
       </c>
       <c r="Y34" t="s">
-        <v>440</v>
+        <v>513</v>
       </c>
       <c r="Z34" t="s">
         <v>782</v>
       </c>
       <c r="AA34">
-        <v>0.99623432132689671</v>
+        <v>0.96942910386940295</v>
       </c>
       <c r="AB34">
-        <v>69.037442340226178</v>
+        <v>560.46642906094564</v>
       </c>
       <c r="AD34" t="s">
         <v>524</v>
@@ -13310,16 +13310,16 @@
         <v>912</v>
       </c>
       <c r="AM34" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AN34" t="s">
         <v>1050</v>
       </c>
-      <c r="AN34" t="s">
-        <v>1051</v>
-      </c>
       <c r="AO34">
-        <v>0.99175391794306234</v>
+        <v>0.99473480482648013</v>
       </c>
       <c r="AP34">
-        <v>151.17817104385733</v>
+        <v>96.528578181196991</v>
       </c>
       <c r="AR34" t="s">
         <v>524</v>
@@ -13352,10 +13352,10 @@
         <v>1246</v>
       </c>
       <c r="BC34">
-        <v>0.99232494426983575</v>
+        <v>0.99203097418485064</v>
       </c>
       <c r="BD34">
-        <v>140.70935505301131</v>
+        <v>146.09880661107059</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -13420,16 +13420,16 @@
         <v>575</v>
       </c>
       <c r="Y35" t="s">
-        <v>456</v>
+        <v>515</v>
       </c>
       <c r="Z35" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AA35">
-        <v>0.99476627594399158</v>
+        <v>0.96192701971480499</v>
       </c>
       <c r="AB35">
-        <v>95.951607693487446</v>
+        <v>698.00463856190902</v>
       </c>
       <c r="AD35" t="s">
         <v>524</v>
@@ -13456,16 +13456,16 @@
         <v>914</v>
       </c>
       <c r="AM35" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AN35" t="s">
         <v>1052</v>
       </c>
-      <c r="AN35" t="s">
-        <v>1053</v>
-      </c>
       <c r="AO35">
-        <v>0.99414234808301016</v>
+        <v>0.99760255773158468</v>
       </c>
       <c r="AP35">
-        <v>107.39028514481463</v>
+        <v>43.953108254279897</v>
       </c>
       <c r="AR35" t="s">
         <v>524</v>
@@ -13498,10 +13498,10 @@
         <v>1248</v>
       </c>
       <c r="BC35">
-        <v>0.98775115723917273</v>
+        <v>0.95713629889852414</v>
       </c>
       <c r="BD35">
-        <v>224.56211728183334</v>
+        <v>785.83452019372396</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -13566,16 +13566,16 @@
         <v>577</v>
       </c>
       <c r="Y36" t="s">
-        <v>463</v>
+        <v>518</v>
       </c>
       <c r="Z36" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AA36">
-        <v>0.99420120324966743</v>
+        <v>0.98823673546715696</v>
       </c>
       <c r="AB36">
-        <v>106.31127375609783</v>
+        <v>215.65984976878829</v>
       </c>
       <c r="AD36" t="s">
         <v>524</v>
@@ -13602,16 +13602,16 @@
         <v>916</v>
       </c>
       <c r="AM36" t="s">
+        <v>1053</v>
+      </c>
+      <c r="AN36" t="s">
         <v>1054</v>
       </c>
-      <c r="AN36" t="s">
-        <v>1055</v>
-      </c>
       <c r="AO36">
-        <v>0.99473480482648013</v>
+        <v>0.99766813121902409</v>
       </c>
       <c r="AP36">
-        <v>96.528578181196991</v>
+        <v>42.750927651225993</v>
       </c>
       <c r="AR36" t="s">
         <v>524</v>
@@ -13641,13 +13641,13 @@
         <v>1249</v>
       </c>
       <c r="BB36" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="BC36">
-        <v>0.99420451954813838</v>
+        <v>0.98806872821788805</v>
       </c>
       <c r="BD36">
-        <v>106.25047495079694</v>
+        <v>218.73998267205184</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -13712,16 +13712,16 @@
         <v>579</v>
       </c>
       <c r="Y37" t="s">
-        <v>448</v>
+        <v>494</v>
       </c>
       <c r="Z37" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AA37">
-        <v>0.99497915241892609</v>
+        <v>0.97762911532019692</v>
       </c>
       <c r="AB37">
-        <v>92.048872319688599</v>
+        <v>410.13288579638987</v>
       </c>
       <c r="AD37" t="s">
         <v>524</v>
@@ -13748,16 +13748,16 @@
         <v>918</v>
       </c>
       <c r="AM37" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AN37" t="s">
         <v>1056</v>
       </c>
-      <c r="AN37" t="s">
-        <v>1057</v>
-      </c>
       <c r="AO37">
-        <v>0.99760255773158468</v>
+        <v>0.99544059907537386</v>
       </c>
       <c r="AP37">
-        <v>43.953108254279897</v>
+        <v>83.589016951479763</v>
       </c>
       <c r="AR37" t="s">
         <v>524</v>
@@ -13784,16 +13784,16 @@
         <v>1191</v>
       </c>
       <c r="BA37" t="s">
+        <v>1250</v>
+      </c>
+      <c r="BB37" t="s">
         <v>1251</v>
       </c>
-      <c r="BB37" t="s">
-        <v>1088</v>
-      </c>
       <c r="BC37">
-        <v>0.99418931598784899</v>
+        <v>0.98946506962487613</v>
       </c>
       <c r="BD37">
-        <v>106.52920688943452</v>
+        <v>193.14039021060518</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -13858,16 +13858,16 @@
         <v>581</v>
       </c>
       <c r="Y38" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
       <c r="Z38" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AA38">
-        <v>0.99401156108202648</v>
+        <v>0.99315026975482257</v>
       </c>
       <c r="AB38">
-        <v>109.78804682951412</v>
+        <v>125.578387828252</v>
       </c>
       <c r="AD38" t="s">
         <v>524</v>
@@ -13894,16 +13894,16 @@
         <v>920</v>
       </c>
       <c r="AM38" t="s">
+        <v>1057</v>
+      </c>
+      <c r="AN38" t="s">
         <v>1058</v>
       </c>
-      <c r="AN38" t="s">
-        <v>1059</v>
-      </c>
       <c r="AO38">
-        <v>0.99766813121902409</v>
+        <v>0.99759498179797546</v>
       </c>
       <c r="AP38">
-        <v>42.750927651225993</v>
+        <v>44.092000370450322</v>
       </c>
       <c r="AR38" t="s">
         <v>524</v>
@@ -13936,10 +13936,10 @@
         <v>1253</v>
       </c>
       <c r="BC38">
-        <v>0.98027195861782945</v>
+        <v>0.99314574070258299</v>
       </c>
       <c r="BD38">
-        <v>361.68075867312689</v>
+        <v>125.66142045264445</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -14004,16 +14004,16 @@
         <v>583</v>
       </c>
       <c r="Y39" t="s">
-        <v>516</v>
+        <v>473</v>
       </c>
       <c r="Z39" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AA39">
-        <v>0.97432735774114165</v>
+        <v>0.99380566729635134</v>
       </c>
       <c r="AB39">
-        <v>470.66510807906917</v>
+        <v>113.56276623355811</v>
       </c>
       <c r="AD39" t="s">
         <v>524</v>
@@ -14040,16 +14040,16 @@
         <v>922</v>
       </c>
       <c r="AM39" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AN39" t="s">
         <v>1060</v>
       </c>
-      <c r="AN39" t="s">
-        <v>1061</v>
-      </c>
       <c r="AO39">
-        <v>0.99544059907537386</v>
+        <v>0.98452519237182756</v>
       </c>
       <c r="AP39">
-        <v>83.589016951479763</v>
+        <v>283.70480651649393</v>
       </c>
       <c r="AR39" t="s">
         <v>524</v>
@@ -14082,10 +14082,10 @@
         <v>1255</v>
       </c>
       <c r="BC39">
-        <v>0.9959052853503485</v>
+        <v>0.99542890407822671</v>
       </c>
       <c r="BD39">
-        <v>75.06976857694373</v>
+        <v>83.803425232511387</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -14150,16 +14150,16 @@
         <v>585</v>
       </c>
       <c r="Y40" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="Z40" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AA40">
-        <v>0.98117083928229931</v>
+        <v>0.9916432660493133</v>
       </c>
       <c r="AB40">
-        <v>345.20127982451362</v>
+        <v>153.20678909592235</v>
       </c>
       <c r="AD40" t="s">
         <v>524</v>
@@ -14186,16 +14186,16 @@
         <v>924</v>
       </c>
       <c r="AM40" t="s">
+        <v>1061</v>
+      </c>
+      <c r="AN40" t="s">
         <v>1062</v>
       </c>
-      <c r="AN40" t="s">
-        <v>1063</v>
-      </c>
       <c r="AO40">
-        <v>0.99759498179797546</v>
+        <v>0.99403730604060547</v>
       </c>
       <c r="AP40">
-        <v>44.092000370450322</v>
+        <v>109.31605592223302</v>
       </c>
       <c r="AR40" t="s">
         <v>524</v>
@@ -14228,10 +14228,10 @@
         <v>1257</v>
       </c>
       <c r="BC40">
-        <v>0.99538398111052984</v>
+        <v>0.98488330873784669</v>
       </c>
       <c r="BD40">
-        <v>84.627012973619784</v>
+        <v>277.13933980614473</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -14296,16 +14296,16 @@
         <v>587</v>
       </c>
       <c r="Y41" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="Z41" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AA41">
-        <v>0.97765910024833902</v>
+        <v>0.99530040212667992</v>
       </c>
       <c r="AB41">
-        <v>409.58316211378531</v>
+        <v>86.159294344200944</v>
       </c>
       <c r="AD41" t="s">
         <v>524</v>
@@ -14332,16 +14332,16 @@
         <v>926</v>
       </c>
       <c r="AM41" t="s">
+        <v>1063</v>
+      </c>
+      <c r="AN41" t="s">
         <v>1064</v>
       </c>
-      <c r="AN41" t="s">
-        <v>1065</v>
-      </c>
       <c r="AO41">
-        <v>0.98599828568941739</v>
+        <v>0.99684152237002188</v>
       </c>
       <c r="AP41">
-        <v>256.69809569401372</v>
+        <v>57.905423216266421</v>
       </c>
       <c r="AR41" t="s">
         <v>524</v>
@@ -14374,10 +14374,10 @@
         <v>1259</v>
       </c>
       <c r="BC41">
-        <v>0.99542890407822671</v>
+        <v>0.99032129621526932</v>
       </c>
       <c r="BD41">
-        <v>83.803425232511387</v>
+        <v>177.44290272006148</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -14442,16 +14442,16 @@
         <v>589</v>
       </c>
       <c r="Y42" t="s">
-        <v>492</v>
+        <v>469</v>
       </c>
       <c r="Z42" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AA42">
-        <v>0.98775140142897844</v>
+        <v>0.98460880049401245</v>
       </c>
       <c r="AB42">
-        <v>224.55764046872929</v>
+        <v>282.17199094310541</v>
       </c>
       <c r="AD42" t="s">
         <v>524</v>
@@ -14478,16 +14478,16 @@
         <v>928</v>
       </c>
       <c r="AM42" t="s">
+        <v>1065</v>
+      </c>
+      <c r="AN42" t="s">
         <v>1066</v>
       </c>
-      <c r="AN42" t="s">
-        <v>1067</v>
-      </c>
       <c r="AO42">
-        <v>0.99500949727727495</v>
+        <v>0.99679967385551038</v>
       </c>
       <c r="AP42">
-        <v>91.492549916626857</v>
+        <v>58.672645982308907</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -14552,16 +14552,16 @@
         <v>591</v>
       </c>
       <c r="Y43" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="Z43" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AA43">
-        <v>0.99563792883070867</v>
+        <v>0.99156821305535681</v>
       </c>
       <c r="AB43">
-        <v>79.971304770340467</v>
+        <v>154.58276065179118</v>
       </c>
       <c r="AD43" t="s">
         <v>524</v>
@@ -14588,16 +14588,16 @@
         <v>930</v>
       </c>
       <c r="AM43" t="s">
+        <v>1067</v>
+      </c>
+      <c r="AN43" t="s">
         <v>1068</v>
       </c>
-      <c r="AN43" t="s">
-        <v>1069</v>
-      </c>
       <c r="AO43">
-        <v>0.99760247912344124</v>
+        <v>0.99083036293819104</v>
       </c>
       <c r="AP43">
-        <v>43.95454940357709</v>
+        <v>168.11001279983091</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -14662,16 +14662,16 @@
         <v>593</v>
       </c>
       <c r="Y44" t="s">
-        <v>420</v>
+        <v>498</v>
       </c>
       <c r="Z44" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AA44">
-        <v>0.99558181127270129</v>
+        <v>0.99098167665935155</v>
       </c>
       <c r="AB44">
-        <v>81.000126667143434</v>
+        <v>165.33592791188894</v>
       </c>
       <c r="AD44" t="s">
         <v>524</v>
@@ -14698,16 +14698,16 @@
         <v>932</v>
       </c>
       <c r="AM44" t="s">
+        <v>1069</v>
+      </c>
+      <c r="AN44" t="s">
         <v>1070</v>
       </c>
-      <c r="AN44" t="s">
-        <v>800</v>
-      </c>
       <c r="AO44">
-        <v>0.95532613069733086</v>
+        <v>0.99710531380540124</v>
       </c>
       <c r="AP44">
-        <v>819.02093721560016</v>
+        <v>53.069246900976879</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -14772,16 +14772,16 @@
         <v>595</v>
       </c>
       <c r="Y45" t="s">
-        <v>520</v>
+        <v>411</v>
       </c>
       <c r="Z45" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AA45">
-        <v>0.99295369446862825</v>
+        <v>0.99634417822754895</v>
       </c>
       <c r="AB45">
-        <v>129.18226807514921</v>
+        <v>67.023399161603095</v>
       </c>
       <c r="AD45" t="s">
         <v>524</v>
@@ -14814,10 +14814,10 @@
         <v>1072</v>
       </c>
       <c r="AO45">
-        <v>0.99693672852577231</v>
+        <v>0.98829989485605374</v>
       </c>
       <c r="AP45">
-        <v>56.159977027506663</v>
+        <v>214.50192763901472</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -14882,16 +14882,16 @@
         <v>597</v>
       </c>
       <c r="Y46" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="Z46" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AA46">
-        <v>0.98092062608337349</v>
+        <v>0.98322732678073066</v>
       </c>
       <c r="AB46">
-        <v>349.78852180481954</v>
+        <v>307.49900901993823</v>
       </c>
       <c r="AD46" t="s">
         <v>524</v>
@@ -14924,10 +14924,10 @@
         <v>1074</v>
       </c>
       <c r="AO46">
-        <v>0.996795372708284</v>
+        <v>0.99663220850609069</v>
       </c>
       <c r="AP46">
-        <v>58.751500348127372</v>
+        <v>61.742844055003644</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -14992,16 +14992,16 @@
         <v>599</v>
       </c>
       <c r="Y47" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="Z47" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="AA47">
-        <v>0.9946911823559148</v>
+        <v>0.99660448707980165</v>
       </c>
       <c r="AB47">
-        <v>97.32832347489618</v>
+        <v>62.251070203636829</v>
       </c>
       <c r="AD47" t="s">
         <v>524</v>
@@ -15034,10 +15034,10 @@
         <v>1076</v>
       </c>
       <c r="AO47">
-        <v>0.99374536027070226</v>
+        <v>0.98934663566509429</v>
       </c>
       <c r="AP47">
-        <v>114.668395037126</v>
+        <v>195.31167947327185</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -15102,16 +15102,16 @@
         <v>601</v>
       </c>
       <c r="Y48" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="Z48" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AA48">
-        <v>0.97539876358704702</v>
+        <v>0.99382195819286057</v>
       </c>
       <c r="AB48">
-        <v>451.02266757080491</v>
+        <v>113.26409979755675</v>
       </c>
       <c r="AD48" t="s">
         <v>524</v>
@@ -15144,10 +15144,10 @@
         <v>1078</v>
       </c>
       <c r="AO48">
-        <v>0.9976540150806753</v>
+        <v>0.99503039970536677</v>
       </c>
       <c r="AP48">
-        <v>43.009723520953628</v>
+        <v>91.109338734942796</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -15212,16 +15212,16 @@
         <v>603</v>
       </c>
       <c r="Y49" t="s">
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="Z49" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AA49">
-        <v>0.99772567527055689</v>
+        <v>0.99710481271463669</v>
       </c>
       <c r="AB49">
-        <v>41.695953373122713</v>
+        <v>53.078433564994235</v>
       </c>
       <c r="AD49" t="s">
         <v>524</v>
@@ -15254,10 +15254,10 @@
         <v>1080</v>
       </c>
       <c r="AO49">
-        <v>0.99671693937496686</v>
+        <v>0.9955955730654259</v>
       </c>
       <c r="AP49">
-        <v>60.189444792275019</v>
+        <v>80.747827133859133</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -15322,16 +15322,16 @@
         <v>605</v>
       </c>
       <c r="Y50" t="s">
-        <v>423</v>
+        <v>521</v>
       </c>
       <c r="Z50" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="AA50">
-        <v>0.99729259940965764</v>
+        <v>0.98313106622136326</v>
       </c>
       <c r="AB50">
-        <v>49.635677489608995</v>
+        <v>309.26378594167363</v>
       </c>
       <c r="AD50" t="s">
         <v>524</v>
@@ -15364,10 +15364,10 @@
         <v>1082</v>
       </c>
       <c r="AO50">
-        <v>0.99244513691456471</v>
+        <v>0.99644815774097173</v>
       </c>
       <c r="AP50">
-        <v>138.50582323297994</v>
+        <v>65.117108082185538</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -15432,16 +15432,16 @@
         <v>607</v>
       </c>
       <c r="Y51" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="Z51" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="AA51">
-        <v>0.99321913659437733</v>
+        <v>0.99459650548991607</v>
       </c>
       <c r="AB51">
-        <v>124.31582910308313</v>
+        <v>99.064066018204684</v>
       </c>
       <c r="AD51" t="s">
         <v>524</v>
@@ -15474,10 +15474,10 @@
         <v>1084</v>
       </c>
       <c r="AO51">
-        <v>0.99729761494442914</v>
+        <v>0.99244513691456471</v>
       </c>
       <c r="AP51">
-        <v>49.543726018799653</v>
+        <v>138.50582323297994</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -15542,16 +15542,16 @@
         <v>609</v>
       </c>
       <c r="Y52" t="s">
-        <v>514</v>
+        <v>430</v>
       </c>
       <c r="Z52" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="AA52">
-        <v>0.96260810713044742</v>
+        <v>0.98625376775139273</v>
       </c>
       <c r="AB52">
-        <v>685.51803594179648</v>
+        <v>252.01425789113298</v>
       </c>
       <c r="AD52" t="s">
         <v>524</v>
@@ -15584,10 +15584,10 @@
         <v>1086</v>
       </c>
       <c r="AO52">
-        <v>0.99478775228549088</v>
+        <v>0.99729761494442914</v>
       </c>
       <c r="AP52">
-        <v>95.557874766001078</v>
+        <v>49.543726018799653</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -15652,16 +15652,16 @@
         <v>611</v>
       </c>
       <c r="Y53" t="s">
-        <v>504</v>
+        <v>474</v>
       </c>
       <c r="Z53" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="AA53">
-        <v>0.95679935803281835</v>
+        <v>0.99417333900805149</v>
       </c>
       <c r="AB53">
-        <v>792.01176939833033</v>
+        <v>106.82211818572355</v>
       </c>
       <c r="AD53" t="s">
         <v>524</v>
@@ -15694,10 +15694,10 @@
         <v>1088</v>
       </c>
       <c r="AO53">
-        <v>0.99729205446773184</v>
+        <v>0.99478775228549088</v>
       </c>
       <c r="AP53">
-        <v>49.645668091582088</v>
+        <v>95.557874766001078</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -15762,16 +15762,16 @@
         <v>613</v>
       </c>
       <c r="Y54" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Z54" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AA54">
-        <v>0.99680369125279411</v>
+        <v>0.99658191580238853</v>
       </c>
       <c r="AB54">
-        <v>58.598993698774343</v>
+        <v>62.664876956210314</v>
       </c>
       <c r="AD54" t="s">
         <v>524</v>
@@ -15804,10 +15804,10 @@
         <v>1090</v>
       </c>
       <c r="AO54">
-        <v>0.98996241922424166</v>
+        <v>0.99729205446773184</v>
       </c>
       <c r="AP54">
-        <v>184.02231422223667</v>
+        <v>49.645668091582088</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -15872,16 +15872,16 @@
         <v>615</v>
       </c>
       <c r="Y55" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="Z55" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AA55">
-        <v>0.9948530685329513</v>
+        <v>0.99549782242326257</v>
       </c>
       <c r="AB55">
-        <v>94.360410229226389</v>
+        <v>82.539922240185263</v>
       </c>
       <c r="AD55" t="s">
         <v>524</v>
@@ -15911,13 +15911,13 @@
         <v>1091</v>
       </c>
       <c r="AN55" t="s">
-        <v>807</v>
+        <v>1092</v>
       </c>
       <c r="AO55">
-        <v>0.97416725971121887</v>
+        <v>0.99620534810300254</v>
       </c>
       <c r="AP55">
-        <v>473.60023862765331</v>
+        <v>69.568618111619969</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -15982,16 +15982,16 @@
         <v>617</v>
       </c>
       <c r="Y56" t="s">
-        <v>441</v>
+        <v>514</v>
       </c>
       <c r="Z56" t="s">
-        <v>803</v>
+        <v>782</v>
       </c>
       <c r="AA56">
-        <v>0.99572841681824009</v>
+        <v>0.96260810713044742</v>
       </c>
       <c r="AB56">
-        <v>78.312358332265575</v>
+        <v>685.51803594179648</v>
       </c>
       <c r="AD56" t="s">
         <v>524</v>
@@ -16018,16 +16018,16 @@
         <v>956</v>
       </c>
       <c r="AM56" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AN56" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AO56">
-        <v>0.99105808324017197</v>
+        <v>0.9961850470371636</v>
       </c>
       <c r="AP56">
-        <v>163.93514059684662</v>
+        <v>69.94080431866837</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -16092,16 +16092,16 @@
         <v>619</v>
       </c>
       <c r="Y57" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="Z57" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="AA57">
-        <v>0.99488680991577683</v>
+        <v>0.95679935803281835</v>
       </c>
       <c r="AB57">
-        <v>93.741818210758069</v>
+        <v>792.01176939833033</v>
       </c>
       <c r="AD57" t="s">
         <v>524</v>
@@ -16128,16 +16128,16 @@
         <v>958</v>
       </c>
       <c r="AM57" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="AN57" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AO57">
-        <v>0.99776894175014486</v>
+        <v>0.99681385284485569</v>
       </c>
       <c r="AP57">
-        <v>40.90273458067751</v>
+        <v>58.41269784431158</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -16202,16 +16202,16 @@
         <v>621</v>
       </c>
       <c r="Y58" t="s">
-        <v>508</v>
+        <v>414</v>
       </c>
       <c r="Z58" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="AA58">
-        <v>0.9895183805448432</v>
+        <v>0.99680369125279411</v>
       </c>
       <c r="AB58">
-        <v>192.16302334454102</v>
+        <v>58.598993698774343</v>
       </c>
       <c r="AD58" t="s">
         <v>524</v>
@@ -16238,16 +16238,16 @@
         <v>960</v>
       </c>
       <c r="AM58" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="AN58" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="AO58">
-        <v>0.99336049451151065</v>
+        <v>0.99274560110857168</v>
       </c>
       <c r="AP58">
-        <v>121.72426728897108</v>
+        <v>132.99731300951822</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -16312,16 +16312,16 @@
         <v>623</v>
       </c>
       <c r="Y59" t="s">
-        <v>495</v>
+        <v>462</v>
       </c>
       <c r="Z59" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="AA59">
-        <v>0.98061830542009054</v>
+        <v>0.9948530685329513</v>
       </c>
       <c r="AB59">
-        <v>355.3310672983406</v>
+        <v>94.360410229226389</v>
       </c>
       <c r="AD59" t="s">
         <v>524</v>
@@ -16348,16 +16348,16 @@
         <v>962</v>
       </c>
       <c r="AM59" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="AN59" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="AO59">
-        <v>0.99527237968252791</v>
+        <v>0.99746043308117838</v>
       </c>
       <c r="AP59">
-        <v>86.673039153654699</v>
+        <v>46.558726845063177</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -16422,16 +16422,16 @@
         <v>625</v>
       </c>
       <c r="Y60" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="Z60" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="AA60">
-        <v>0.97537853020161625</v>
+        <v>0.99572841681824009</v>
       </c>
       <c r="AB60">
-        <v>451.39361297036953</v>
+        <v>78.312358332265575</v>
       </c>
       <c r="AD60" t="s">
         <v>524</v>
@@ -16458,16 +16458,16 @@
         <v>964</v>
       </c>
       <c r="AM60" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="AN60" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AO60">
-        <v>0.9917253583369573</v>
+        <v>0.98599828568941739</v>
       </c>
       <c r="AP60">
-        <v>151.70176382244892</v>
+        <v>256.69809569401372</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -16532,16 +16532,16 @@
         <v>627</v>
       </c>
       <c r="Y61" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="Z61" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="AA61">
-        <v>0.99198935558098356</v>
+        <v>0.99488680991577683</v>
       </c>
       <c r="AB61">
-        <v>146.8618143486346</v>
+        <v>93.741818210758069</v>
       </c>
       <c r="AD61" t="s">
         <v>524</v>
@@ -16568,16 +16568,16 @@
         <v>966</v>
       </c>
       <c r="AM61" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="AN61" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="AO61">
-        <v>0.97020178001960844</v>
+        <v>0.99500949727727495</v>
       </c>
       <c r="AP61">
-        <v>546.30069964051177</v>
+        <v>91.492549916626857</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -16642,16 +16642,16 @@
         <v>629</v>
       </c>
       <c r="Y62" t="s">
-        <v>452</v>
+        <v>501</v>
       </c>
       <c r="Z62" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="AA62">
-        <v>0.99528785955431354</v>
+        <v>0.95261480241426988</v>
       </c>
       <c r="AB62">
-        <v>86.389241504250975</v>
+        <v>868.72862240505196</v>
       </c>
       <c r="AD62" t="s">
         <v>524</v>
@@ -16678,16 +16678,16 @@
         <v>968</v>
       </c>
       <c r="AM62" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="AN62" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="AO62">
-        <v>0.99352359657507616</v>
+        <v>0.99760247912344124</v>
       </c>
       <c r="AP62">
-        <v>118.7340627902709</v>
+        <v>43.95454940357709</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -16752,16 +16752,16 @@
         <v>631</v>
       </c>
       <c r="Y63" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="Z63" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="AA63">
-        <v>0.99008735429887684</v>
+        <v>0.96316770855847034</v>
       </c>
       <c r="AB63">
-        <v>181.7318378539255</v>
+        <v>675.25867642804383</v>
       </c>
       <c r="AD63" t="s">
         <v>524</v>
@@ -16788,16 +16788,16 @@
         <v>970</v>
       </c>
       <c r="AM63" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AN63" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AO63">
-        <v>0.99532453653339104</v>
+        <v>0.98134982200735632</v>
       </c>
       <c r="AP63">
-        <v>85.716830221163534</v>
+        <v>341.91992986513412</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -16862,16 +16862,16 @@
         <v>633</v>
       </c>
       <c r="Y64" t="s">
-        <v>427</v>
+        <v>511</v>
       </c>
       <c r="Z64" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="AA64">
-        <v>0.99219431421335524</v>
+        <v>0.99751741634821878</v>
       </c>
       <c r="AB64">
-        <v>143.10423942182081</v>
+        <v>45.514033615989625</v>
       </c>
       <c r="AD64" t="s">
         <v>524</v>
@@ -16898,16 +16898,16 @@
         <v>972</v>
       </c>
       <c r="AM64" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="AN64" t="s">
-        <v>1109</v>
+        <v>798</v>
       </c>
       <c r="AO64">
-        <v>0.99593828267147511</v>
+        <v>0.98674094240398891</v>
       </c>
       <c r="AP64">
-        <v>74.464817689622748</v>
+        <v>243.0827225935364</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -16972,16 +16972,16 @@
         <v>635</v>
       </c>
       <c r="Y65" t="s">
-        <v>489</v>
+        <v>426</v>
       </c>
       <c r="Z65" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="AA65">
-        <v>0.99107116626800151</v>
+        <v>0.9921930449834182</v>
       </c>
       <c r="AB65">
-        <v>163.69528508663959</v>
+        <v>143.1275086373324</v>
       </c>
       <c r="AD65" t="s">
         <v>524</v>
@@ -17014,10 +17014,10 @@
         <v>1111</v>
       </c>
       <c r="AO65">
-        <v>0.98134982200735632</v>
+        <v>0.9959346869215373</v>
       </c>
       <c r="AP65">
-        <v>341.91992986513412</v>
+        <v>74.530739771815789</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -17082,16 +17082,16 @@
         <v>637</v>
       </c>
       <c r="Y66" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="Z66" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="AA66">
-        <v>0.99653079856255411</v>
+        <v>0.97046839264048923</v>
       </c>
       <c r="AB66">
-        <v>63.602026353175077</v>
+        <v>541.41280159103133</v>
       </c>
       <c r="AD66" t="s">
         <v>524</v>
@@ -17121,13 +17121,13 @@
         <v>1112</v>
       </c>
       <c r="AN66" t="s">
-        <v>842</v>
+        <v>1113</v>
       </c>
       <c r="AO66">
-        <v>0.98674094240398891</v>
+        <v>0.9976320377495026</v>
       </c>
       <c r="AP66">
-        <v>243.0827225935364</v>
+        <v>43.412641259119624</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -17192,16 +17192,16 @@
         <v>639</v>
       </c>
       <c r="Y67" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Z67" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="AA67">
-        <v>0.99516969310216208</v>
+        <v>0.98262799295672731</v>
       </c>
       <c r="AB67">
-        <v>88.555626460362205</v>
+        <v>318.48679579333231</v>
       </c>
       <c r="AD67" t="s">
         <v>524</v>
@@ -17228,16 +17228,16 @@
         <v>978</v>
       </c>
       <c r="AM67" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="AN67" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="AO67">
-        <v>0.9959346869215373</v>
+        <v>0.99433447571906541</v>
       </c>
       <c r="AP67">
-        <v>74.530739771815789</v>
+        <v>103.86794515046822</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -17302,16 +17302,16 @@
         <v>641</v>
       </c>
       <c r="Y68" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="Z68" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="AA68">
-        <v>0.98827949012946181</v>
+        <v>0.99339186524799883</v>
       </c>
       <c r="AB68">
-        <v>214.8760142931996</v>
+        <v>121.14913712002206</v>
       </c>
       <c r="AD68" t="s">
         <v>524</v>
@@ -17338,16 +17338,16 @@
         <v>980</v>
       </c>
       <c r="AM68" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="AN68" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="AO68">
-        <v>0.9976320377495026</v>
+        <v>0.99688290256322298</v>
       </c>
       <c r="AP68">
-        <v>43.412641259119624</v>
+        <v>57.146786340912868</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -17412,16 +17412,16 @@
         <v>643</v>
       </c>
       <c r="Y69" t="s">
-        <v>422</v>
+        <v>459</v>
       </c>
       <c r="Z69" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="AA69">
-        <v>0.99780983219878738</v>
+        <v>0.99585747088130616</v>
       </c>
       <c r="AB69">
-        <v>40.153076355563911</v>
+        <v>75.946367176053897</v>
       </c>
       <c r="AD69" t="s">
         <v>524</v>
@@ -17448,16 +17448,16 @@
         <v>982</v>
       </c>
       <c r="AM69" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AN69" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="AO69">
-        <v>0.99433447571906541</v>
+        <v>0.99569050067699549</v>
       </c>
       <c r="AP69">
-        <v>103.86794515046822</v>
+        <v>79.007487588415231</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -17522,16 +17522,16 @@
         <v>645</v>
       </c>
       <c r="Y70" t="s">
-        <v>437</v>
+        <v>500</v>
       </c>
       <c r="Z70" t="s">
-        <v>817</v>
+        <v>791</v>
       </c>
       <c r="AA70">
-        <v>0.99478593896263345</v>
+        <v>0.93980266520001188</v>
       </c>
       <c r="AB70">
-        <v>95.59111901838736</v>
+        <v>1103.617804666449</v>
       </c>
       <c r="AD70" t="s">
         <v>524</v>
@@ -17558,16 +17558,16 @@
         <v>984</v>
       </c>
       <c r="AM70" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AN70" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="AO70">
-        <v>0.99688290256322298</v>
+        <v>0.97020178001960844</v>
       </c>
       <c r="AP70">
-        <v>57.146786340912868</v>
+        <v>546.30069964051177</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -17632,16 +17632,16 @@
         <v>647</v>
       </c>
       <c r="Y71" t="s">
-        <v>466</v>
+        <v>512</v>
       </c>
       <c r="Z71" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="AA71">
-        <v>0.99431447054153432</v>
+        <v>0.99645756936252694</v>
       </c>
       <c r="AB71">
-        <v>104.23470673853728</v>
+        <v>64.944561687006995</v>
       </c>
       <c r="AD71" t="s">
         <v>524</v>
@@ -17668,16 +17668,16 @@
         <v>986</v>
       </c>
       <c r="AM71" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="AN71" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="AO71">
-        <v>0.99569050067699549</v>
+        <v>0.99352359657507616</v>
       </c>
       <c r="AP71">
-        <v>79.007487588415231</v>
+        <v>118.7340627902709</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -17742,16 +17742,16 @@
         <v>649</v>
       </c>
       <c r="Y72" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="Z72" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="AA72">
-        <v>0.99649132983250632</v>
+        <v>0.99758516433905853</v>
       </c>
       <c r="AB72">
-        <v>64.325619737385011</v>
+        <v>44.271987117260508</v>
       </c>
       <c r="AD72" t="s">
         <v>524</v>
@@ -17778,16 +17778,16 @@
         <v>988</v>
       </c>
       <c r="AM72" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="AN72" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="AO72">
-        <v>0.98934663566509429</v>
+        <v>0.99532453653339104</v>
       </c>
       <c r="AP72">
-        <v>195.31167947327185</v>
+        <v>85.716830221163534</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -17852,16 +17852,16 @@
         <v>651</v>
       </c>
       <c r="Y73" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="Z73" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="AA73">
-        <v>0.9925766880786181</v>
+        <v>0.99267004448650609</v>
       </c>
       <c r="AB73">
-        <v>136.09405189200152</v>
+        <v>134.38251774738842</v>
       </c>
       <c r="AD73" t="s">
         <v>524</v>
@@ -17888,16 +17888,16 @@
         <v>990</v>
       </c>
       <c r="AM73" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="AN73" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="AO73">
-        <v>0.99503039970536677</v>
+        <v>0.99593828267147511</v>
       </c>
       <c r="AP73">
-        <v>91.109338734942796</v>
+        <v>74.464817689622748</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -17962,16 +17962,16 @@
         <v>653</v>
       </c>
       <c r="Y74" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="Z74" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="AA74">
-        <v>0.99638451167998066</v>
+        <v>0.99623432132689671</v>
       </c>
       <c r="AB74">
-        <v>66.283952533688392</v>
+        <v>69.037442340226178</v>
       </c>
       <c r="AD74" t="s">
         <v>524</v>
@@ -17998,16 +17998,16 @@
         <v>992</v>
       </c>
       <c r="AM74" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="AN74" t="s">
-        <v>1128</v>
+        <v>802</v>
       </c>
       <c r="AO74">
-        <v>0.9955955730654259</v>
+        <v>0.95532613069733086</v>
       </c>
       <c r="AP74">
-        <v>80.747827133859133</v>
+        <v>819.02093721560016</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -18072,16 +18072,16 @@
         <v>655</v>
       </c>
       <c r="Y75" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="Z75" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="AA75">
-        <v>0.99306919419080486</v>
+        <v>0.99476627594399158</v>
       </c>
       <c r="AB75">
-        <v>127.06477316857749</v>
+        <v>95.951607693487446</v>
       </c>
       <c r="AD75" t="s">
         <v>524</v>
@@ -18114,10 +18114,10 @@
         <v>1130</v>
       </c>
       <c r="AO75">
-        <v>0.99644815774097173</v>
+        <v>0.99693672852577231</v>
       </c>
       <c r="AP75">
-        <v>65.117108082185538</v>
+        <v>56.159977027506663</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -18182,16 +18182,16 @@
         <v>657</v>
       </c>
       <c r="Y76" t="s">
-        <v>498</v>
+        <v>463</v>
       </c>
       <c r="Z76" t="s">
-        <v>778</v>
+        <v>819</v>
       </c>
       <c r="AA76">
-        <v>0.99098167665935155</v>
+        <v>0.99420120324966743</v>
       </c>
       <c r="AB76">
-        <v>165.33592791188894</v>
+        <v>106.31127375609783</v>
       </c>
       <c r="AD76" t="s">
         <v>524</v>
@@ -18224,10 +18224,10 @@
         <v>1132</v>
       </c>
       <c r="AO76">
-        <v>0.98589595763902149</v>
+        <v>0.996795372708284</v>
       </c>
       <c r="AP76">
-        <v>258.57410995127316</v>
+        <v>58.751500348127372</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -18292,16 +18292,16 @@
         <v>659</v>
       </c>
       <c r="Y77" t="s">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="Z77" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="AA77">
-        <v>0.99634417822754895</v>
+        <v>0.99497915241892609</v>
       </c>
       <c r="AB77">
-        <v>67.023399161603095</v>
+        <v>92.048872319688599</v>
       </c>
       <c r="AD77" t="s">
         <v>524</v>
@@ -18334,10 +18334,10 @@
         <v>1134</v>
       </c>
       <c r="AO77">
-        <v>0.99554924619735208</v>
+        <v>0.99374536027070226</v>
       </c>
       <c r="AP77">
-        <v>81.597153048545437</v>
+        <v>114.668395037126</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -18402,16 +18402,16 @@
         <v>661</v>
       </c>
       <c r="Y78" t="s">
-        <v>483</v>
+        <v>443</v>
       </c>
       <c r="Z78" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="AA78">
-        <v>0.98322732678073066</v>
+        <v>0.99401156108202648</v>
       </c>
       <c r="AB78">
-        <v>307.49900901993823</v>
+        <v>109.78804682951412</v>
       </c>
       <c r="AD78" t="s">
         <v>524</v>
@@ -18444,10 +18444,10 @@
         <v>1136</v>
       </c>
       <c r="AO78">
-        <v>0.99534886842510228</v>
+        <v>0.9976540150806753</v>
       </c>
       <c r="AP78">
-        <v>85.270745539791065</v>
+        <v>43.009723520953628</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -18512,16 +18512,16 @@
         <v>663</v>
       </c>
       <c r="Y79" t="s">
-        <v>418</v>
+        <v>506</v>
       </c>
       <c r="Z79" t="s">
-        <v>825</v>
+        <v>791</v>
       </c>
       <c r="AA79">
-        <v>0.99660448707980165</v>
+        <v>0.97244982574001193</v>
       </c>
       <c r="AB79">
-        <v>62.251070203636829</v>
+        <v>505.08652809978111</v>
       </c>
       <c r="AD79" t="s">
         <v>524</v>
@@ -18554,10 +18554,10 @@
         <v>1138</v>
       </c>
       <c r="AO79">
-        <v>0.99488275259079373</v>
+        <v>0.99671693937496686</v>
       </c>
       <c r="AP79">
-        <v>93.81620250211445</v>
+        <v>60.189444792275019</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -18622,16 +18622,16 @@
         <v>665</v>
       </c>
       <c r="Y80" t="s">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="Z80" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="AA80">
-        <v>0.99382195819286057</v>
+        <v>0.99020196511745218</v>
       </c>
       <c r="AB80">
-        <v>113.26409979755675</v>
+        <v>179.63063951337628</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -18696,16 +18696,16 @@
         <v>667</v>
       </c>
       <c r="Y81" t="s">
-        <v>453</v>
+        <v>496</v>
       </c>
       <c r="Z81" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="AA81">
-        <v>0.99710481271463669</v>
+        <v>0.99299353576618077</v>
       </c>
       <c r="AB81">
-        <v>53.078433564994235</v>
+        <v>128.45184428668603</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -18770,16 +18770,16 @@
         <v>669</v>
       </c>
       <c r="Y82" t="s">
-        <v>472</v>
+        <v>432</v>
       </c>
       <c r="Z82" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="AA82">
-        <v>0.99150508017022432</v>
+        <v>0.98731404165703462</v>
       </c>
       <c r="AB82">
-        <v>155.74019687921984</v>
+        <v>232.57590295436526</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -18844,16 +18844,16 @@
         <v>671</v>
       </c>
       <c r="Y83" t="s">
-        <v>439</v>
+        <v>471</v>
       </c>
       <c r="Z83" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="AA83">
-        <v>0.99591694828752353</v>
+        <v>0.99505763323061869</v>
       </c>
       <c r="AB83">
-        <v>74.855948062068691</v>
+        <v>90.610057438657108</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -18918,16 +18918,16 @@
         <v>673</v>
       </c>
       <c r="Y84" t="s">
-        <v>501</v>
+        <v>419</v>
       </c>
       <c r="Z84" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="AA84">
-        <v>0.95261480241426988</v>
+        <v>0.9946350729064154</v>
       </c>
       <c r="AB84">
-        <v>868.72862240505196</v>
+        <v>98.356996715718111</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -18992,16 +18992,16 @@
         <v>675</v>
       </c>
       <c r="Y85" t="s">
-        <v>502</v>
+        <v>445</v>
       </c>
       <c r="Z85" t="s">
-        <v>778</v>
+        <v>827</v>
       </c>
       <c r="AA85">
-        <v>0.96316770855847034</v>
+        <v>0.99494501873633134</v>
       </c>
       <c r="AB85">
-        <v>675.25867642804383</v>
+        <v>92.674656500591539</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -19066,16 +19066,16 @@
         <v>677</v>
       </c>
       <c r="Y86" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="Z86" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="AA86">
-        <v>0.99751741634821878</v>
+        <v>0.9895183805448432</v>
       </c>
       <c r="AB86">
-        <v>45.514033615989625</v>
+        <v>192.16302334454102</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -19140,16 +19140,16 @@
         <v>679</v>
       </c>
       <c r="Y87" t="s">
-        <v>426</v>
+        <v>495</v>
       </c>
       <c r="Z87" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="AA87">
-        <v>0.9921930449834182</v>
+        <v>0.98061830542009054</v>
       </c>
       <c r="AB87">
-        <v>143.1275086373324</v>
+        <v>355.3310672983406</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -19214,16 +19214,16 @@
         <v>681</v>
       </c>
       <c r="Y88" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Z88" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="AA88">
-        <v>0.97046839264048923</v>
+        <v>0.97537853020161625</v>
       </c>
       <c r="AB88">
-        <v>541.41280159103133</v>
+        <v>451.39361297036953</v>
       </c>
     </row>
     <row r="89" spans="2:28">
@@ -19288,16 +19288,16 @@
         <v>683</v>
       </c>
       <c r="Y89" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="Z89" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="AA89">
-        <v>0.98262799295672731</v>
+        <v>0.99198935558098356</v>
       </c>
       <c r="AB89">
-        <v>318.48679579333231</v>
+        <v>146.8618143486346</v>
       </c>
     </row>
     <row r="90" spans="2:28">
@@ -19362,16 +19362,16 @@
         <v>685</v>
       </c>
       <c r="Y90" t="s">
-        <v>477</v>
+        <v>452</v>
       </c>
       <c r="Z90" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="AA90">
-        <v>0.99339186524799883</v>
+        <v>0.99528785955431354</v>
       </c>
       <c r="AB90">
-        <v>121.14913712002206</v>
+        <v>86.389241504250975</v>
       </c>
     </row>
     <row r="91" spans="2:28">
@@ -19436,16 +19436,16 @@
         <v>687</v>
       </c>
       <c r="Y91" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
       <c r="Z91" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="AA91">
-        <v>0.99585747088130616</v>
+        <v>0.99150508017022432</v>
       </c>
       <c r="AB91">
-        <v>75.946367176053897</v>
+        <v>155.74019687921984</v>
       </c>
     </row>
     <row r="92" spans="2:28">
@@ -19510,16 +19510,16 @@
         <v>689</v>
       </c>
       <c r="Y92" t="s">
-        <v>503</v>
+        <v>439</v>
       </c>
       <c r="Z92" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="AA92">
-        <v>0.96520767961718001</v>
+        <v>0.99591694828752353</v>
       </c>
       <c r="AB92">
-        <v>637.85920701836687</v>
+        <v>74.855948062068691</v>
       </c>
     </row>
     <row r="93" spans="2:28">
@@ -19584,16 +19584,16 @@
         <v>691</v>
       </c>
       <c r="Y93" t="s">
-        <v>412</v>
+        <v>520</v>
       </c>
       <c r="Z93" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="AA93">
-        <v>0.98762421667584677</v>
+        <v>0.99295369446862825</v>
       </c>
       <c r="AB93">
-        <v>226.88936094280919</v>
+        <v>129.18226807514921</v>
       </c>
     </row>
     <row r="94" spans="2:28">
@@ -19658,16 +19658,16 @@
         <v>693</v>
       </c>
       <c r="Y94" t="s">
-        <v>436</v>
+        <v>493</v>
       </c>
       <c r="Z94" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="AA94">
-        <v>0.99519314522306834</v>
+        <v>0.98092062608337349</v>
       </c>
       <c r="AB94">
-        <v>88.125670910414172</v>
+        <v>349.78852180481954</v>
       </c>
     </row>
     <row r="95" spans="2:28">
@@ -19732,16 +19732,16 @@
         <v>695</v>
       </c>
       <c r="Y95" t="s">
-        <v>444</v>
+        <v>408</v>
       </c>
       <c r="Z95" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="AA95">
-        <v>0.99377714174527498</v>
+        <v>0.9946911823559148</v>
       </c>
       <c r="AB95">
-        <v>114.08573466995766</v>
+        <v>97.32832347489618</v>
       </c>
     </row>
     <row r="96" spans="2:28">
@@ -19806,16 +19806,16 @@
         <v>697</v>
       </c>
       <c r="Y96" t="s">
-        <v>521</v>
+        <v>476</v>
       </c>
       <c r="Z96" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="AA96">
-        <v>0.98313106622136326</v>
+        <v>0.97539876358704702</v>
       </c>
       <c r="AB96">
-        <v>309.26378594167363</v>
+        <v>451.02266757080491</v>
       </c>
     </row>
     <row r="97" spans="2:28">
@@ -19880,16 +19880,16 @@
         <v>699</v>
       </c>
       <c r="Y97" t="s">
-        <v>499</v>
+        <v>417</v>
       </c>
       <c r="Z97" t="s">
-        <v>778</v>
+        <v>839</v>
       </c>
       <c r="AA97">
-        <v>0.99459650548991607</v>
+        <v>0.99772567527055689</v>
       </c>
       <c r="AB97">
-        <v>99.064066018204684</v>
+        <v>41.695953373122713</v>
       </c>
     </row>
     <row r="98" spans="2:28">
@@ -19954,16 +19954,16 @@
         <v>701</v>
       </c>
       <c r="Y98" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="Z98" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="AA98">
-        <v>0.98625376775139273</v>
+        <v>0.99729259940965764</v>
       </c>
       <c r="AB98">
-        <v>252.01425789113298</v>
+        <v>49.635677489608995</v>
       </c>
     </row>
     <row r="99" spans="2:28">
@@ -20028,16 +20028,16 @@
         <v>703</v>
       </c>
       <c r="Y99" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="Z99" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="AA99">
-        <v>0.99417333900805149</v>
+        <v>0.99321913659437733</v>
       </c>
       <c r="AB99">
-        <v>106.82211818572355</v>
+        <v>124.31582910308313</v>
       </c>
     </row>
     <row r="100" spans="2:28">
@@ -20102,16 +20102,16 @@
         <v>705</v>
       </c>
       <c r="Y100" t="s">
-        <v>416</v>
+        <v>516</v>
       </c>
       <c r="Z100" t="s">
-        <v>844</v>
+        <v>782</v>
       </c>
       <c r="AA100">
-        <v>0.99658191580238853</v>
+        <v>0.97432735774114165</v>
       </c>
       <c r="AB100">
-        <v>62.664876956210314</v>
+        <v>470.66510807906917</v>
       </c>
     </row>
     <row r="101" spans="2:28">
@@ -20176,16 +20176,16 @@
         <v>707</v>
       </c>
       <c r="Y101" t="s">
-        <v>446</v>
+        <v>490</v>
       </c>
       <c r="Z101" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="AA101">
-        <v>0.99549782242326257</v>
+        <v>0.98117083928229931</v>
       </c>
       <c r="AB101">
-        <v>82.539922240185263</v>
+        <v>345.20127982451362</v>
       </c>
     </row>
     <row r="102" spans="2:28">
@@ -20250,16 +20250,16 @@
         <v>709</v>
       </c>
       <c r="Y102" t="s">
-        <v>513</v>
+        <v>482</v>
       </c>
       <c r="Z102" t="s">
-        <v>787</v>
+        <v>843</v>
       </c>
       <c r="AA102">
-        <v>0.96942910386940295</v>
+        <v>0.97765910024833902</v>
       </c>
       <c r="AB102">
-        <v>560.46642906094564</v>
+        <v>409.58316211378531</v>
       </c>
     </row>
     <row r="103" spans="2:28">
@@ -20324,16 +20324,16 @@
         <v>711</v>
       </c>
       <c r="Y103" t="s">
-        <v>515</v>
+        <v>492</v>
       </c>
       <c r="Z103" t="s">
-        <v>787</v>
+        <v>844</v>
       </c>
       <c r="AA103">
-        <v>0.96192701971480499</v>
+        <v>0.98775140142897844</v>
       </c>
       <c r="AB103">
-        <v>698.00463856190902</v>
+        <v>224.55764046872929</v>
       </c>
     </row>
     <row r="104" spans="2:28">
@@ -20398,16 +20398,16 @@
         <v>713</v>
       </c>
       <c r="Y104" t="s">
-        <v>518</v>
+        <v>478</v>
       </c>
       <c r="Z104" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AA104">
-        <v>0.98823673546715696</v>
+        <v>0.99563792883070867</v>
       </c>
       <c r="AB104">
-        <v>215.65984976878829</v>
+        <v>79.971304770340467</v>
       </c>
     </row>
     <row r="105" spans="2:28">
@@ -20472,16 +20472,16 @@
         <v>715</v>
       </c>
       <c r="Y105" t="s">
-        <v>494</v>
+        <v>420</v>
       </c>
       <c r="Z105" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AA105">
-        <v>0.97762911532019692</v>
+        <v>0.99558181127270129</v>
       </c>
       <c r="AB105">
-        <v>410.13288579638987</v>
+        <v>81.000126667143434</v>
       </c>
     </row>
     <row r="106" spans="2:28">
@@ -20546,16 +20546,16 @@
         <v>717</v>
       </c>
       <c r="Y106" t="s">
-        <v>413</v>
+        <v>519</v>
       </c>
       <c r="Z106" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AA106">
-        <v>0.99315026975482257</v>
+        <v>0.99506672623055659</v>
       </c>
       <c r="AB106">
-        <v>125.578387828252</v>
+        <v>90.443352439796072</v>
       </c>
     </row>
     <row r="107" spans="2:28">
@@ -20620,16 +20620,16 @@
         <v>719</v>
       </c>
       <c r="Y107" t="s">
-        <v>473</v>
+        <v>509</v>
       </c>
       <c r="Z107" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="AA107">
-        <v>0.99380566729635134</v>
+        <v>0.98810060695535451</v>
       </c>
       <c r="AB107">
-        <v>113.56276623355811</v>
+        <v>218.15553915183366</v>
       </c>
     </row>
     <row r="108" spans="2:28">
@@ -20694,16 +20694,16 @@
         <v>721</v>
       </c>
       <c r="Y108" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="Z108" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AA108">
-        <v>0.9916432660493133</v>
+        <v>0.98820036495460695</v>
       </c>
       <c r="AB108">
-        <v>153.20678909592235</v>
+        <v>216.32664249887239</v>
       </c>
     </row>
     <row r="109" spans="2:28">
@@ -20768,16 +20768,16 @@
         <v>723</v>
       </c>
       <c r="Y109" t="s">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="Z109" t="s">
-        <v>851</v>
+        <v>822</v>
       </c>
       <c r="AA109">
-        <v>0.99530040212667992</v>
+        <v>0.97404342257401955</v>
       </c>
       <c r="AB109">
-        <v>86.159294344200944</v>
+        <v>475.8705861429753</v>
       </c>
     </row>
     <row r="110" spans="2:28">
@@ -20842,16 +20842,16 @@
         <v>725</v>
       </c>
       <c r="Y110" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="Z110" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="AA110">
-        <v>0.98460880049401245</v>
+        <v>0.99284309609540211</v>
       </c>
       <c r="AB110">
-        <v>282.17199094310541</v>
+        <v>131.20990491762768</v>
       </c>
     </row>
     <row r="111" spans="2:28">
@@ -20916,16 +20916,16 @@
         <v>727</v>
       </c>
       <c r="Y111" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="Z111" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="AA111">
-        <v>0.99156821305535681</v>
+        <v>0.99247189917622181</v>
       </c>
       <c r="AB111">
-        <v>154.58276065179118</v>
+        <v>138.01518176926754</v>
       </c>
     </row>
     <row r="112" spans="2:28">
@@ -20990,16 +20990,16 @@
         <v>729</v>
       </c>
       <c r="Y112" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="Z112" t="s">
-        <v>778</v>
+        <v>852</v>
       </c>
       <c r="AA112">
-        <v>0.97244982574001193</v>
+        <v>0.98563153879963317</v>
       </c>
       <c r="AB112">
-        <v>505.08652809978111</v>
+        <v>263.42178867339101</v>
       </c>
     </row>
     <row r="113" spans="2:28">
@@ -21064,16 +21064,16 @@
         <v>731</v>
       </c>
       <c r="Y113" t="s">
-        <v>497</v>
+        <v>421</v>
       </c>
       <c r="Z113" t="s">
-        <v>768</v>
+        <v>853</v>
       </c>
       <c r="AA113">
-        <v>0.99020196511745218</v>
+        <v>0.99704166323096854</v>
       </c>
       <c r="AB113">
-        <v>179.63063951337628</v>
+        <v>54.23617409891024</v>
       </c>
     </row>
     <row r="114" spans="2:28">
@@ -21138,16 +21138,16 @@
         <v>733</v>
       </c>
       <c r="Y114" t="s">
-        <v>496</v>
+        <v>461</v>
       </c>
       <c r="Z114" t="s">
         <v>854</v>
       </c>
       <c r="AA114">
-        <v>0.99299353576618077</v>
+        <v>0.99529226044395613</v>
       </c>
       <c r="AB114">
-        <v>128.45184428668603</v>
+        <v>86.308558527470979</v>
       </c>
     </row>
     <row r="115" spans="2:28">
@@ -21212,16 +21212,16 @@
         <v>735</v>
       </c>
       <c r="Y115" t="s">
-        <v>432</v>
+        <v>467</v>
       </c>
       <c r="Z115" t="s">
         <v>855</v>
       </c>
       <c r="AA115">
-        <v>0.98731404165703462</v>
+        <v>0.99324569511004301</v>
       </c>
       <c r="AB115">
-        <v>232.57590295436526</v>
+        <v>123.82892298254488</v>
       </c>
     </row>
     <row r="116" spans="2:28">
@@ -21286,16 +21286,16 @@
         <v>737</v>
       </c>
       <c r="Y116" t="s">
-        <v>471</v>
+        <v>424</v>
       </c>
       <c r="Z116" t="s">
         <v>856</v>
       </c>
       <c r="AA116">
-        <v>0.99505763323061869</v>
+        <v>0.99731037386855248</v>
       </c>
       <c r="AB116">
-        <v>90.610057438657108</v>
+        <v>49.309812409870183</v>
       </c>
     </row>
     <row r="117" spans="2:28">
@@ -21360,16 +21360,16 @@
         <v>739</v>
       </c>
       <c r="Y117" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="Z117" t="s">
         <v>857</v>
       </c>
       <c r="AA117">
-        <v>0.9946350729064154</v>
+        <v>0.99465722366873854</v>
       </c>
       <c r="AB117">
-        <v>98.356996715718111</v>
+        <v>97.950899406460266</v>
       </c>
     </row>
     <row r="118" spans="2:28">
@@ -21434,16 +21434,16 @@
         <v>741</v>
       </c>
       <c r="Y118" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="Z118" t="s">
         <v>858</v>
       </c>
       <c r="AA118">
-        <v>0.99494501873633134</v>
+        <v>0.99703280926921656</v>
       </c>
       <c r="AB118">
-        <v>92.674656500591539</v>
+        <v>54.398496731030697</v>
       </c>
     </row>
     <row r="119" spans="2:28">
@@ -21970,7 +21970,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{091451A0-BD85-43A2-AAF1-9A4895C4AF78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B9A89F7-CFC6-4CBF-974A-FC95685EC0E9}">
   <dimension ref="B9:Z79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -22082,7 +22082,7 @@
         <v>1260</v>
       </c>
       <c r="K11" t="s">
-        <v>1102</v>
+        <v>1120</v>
       </c>
       <c r="L11">
         <v>10.563746678268352</v>
@@ -22115,7 +22115,7 @@
         <v>1398</v>
       </c>
       <c r="X11" t="s">
-        <v>1201</v>
+        <v>1230</v>
       </c>
       <c r="Y11">
         <v>54.979500000000002</v>
@@ -22150,7 +22150,7 @@
         <v>1262</v>
       </c>
       <c r="K12" t="s">
-        <v>1091</v>
+        <v>1038</v>
       </c>
       <c r="L12">
         <v>7.4816578037471135</v>
@@ -22183,7 +22183,7 @@
         <v>1400</v>
       </c>
       <c r="X12" t="s">
-        <v>1239</v>
+        <v>1220</v>
       </c>
       <c r="Y12">
         <v>0.74099999999999999</v>
@@ -22218,7 +22218,7 @@
         <v>1264</v>
       </c>
       <c r="K13" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="L13">
         <v>4.7713910333636482</v>
@@ -22251,7 +22251,7 @@
         <v>1402</v>
       </c>
       <c r="X13" t="s">
-        <v>1222</v>
+        <v>1201</v>
       </c>
       <c r="Y13">
         <v>36.586500000000001</v>
@@ -22286,7 +22286,7 @@
         <v>1266</v>
       </c>
       <c r="K14" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="L14">
         <v>12.404103898825962</v>
@@ -22319,7 +22319,7 @@
         <v>1404</v>
       </c>
       <c r="X14" t="s">
-        <v>1232</v>
+        <v>1258</v>
       </c>
       <c r="Y14">
         <v>53.094000000000001</v>
@@ -22354,7 +22354,7 @@
         <v>1268</v>
       </c>
       <c r="K15" t="s">
-        <v>1064</v>
+        <v>1101</v>
       </c>
       <c r="L15">
         <v>6.1276234637439133</v>
@@ -22387,7 +22387,7 @@
         <v>1406</v>
       </c>
       <c r="X15" t="s">
-        <v>1213</v>
+        <v>1245</v>
       </c>
       <c r="Y15">
         <v>55.56</v>
@@ -22422,7 +22422,7 @@
         <v>1270</v>
       </c>
       <c r="K16" t="s">
-        <v>1048</v>
+        <v>1014</v>
       </c>
       <c r="L16">
         <v>2.2195844391122765</v>
@@ -22455,7 +22455,7 @@
         <v>1408</v>
       </c>
       <c r="X16" t="s">
-        <v>1209</v>
+        <v>1252</v>
       </c>
       <c r="Y16">
         <v>43.858499999999999</v>
@@ -22490,7 +22490,7 @@
         <v>1272</v>
       </c>
       <c r="K17" t="s">
-        <v>1044</v>
+        <v>1010</v>
       </c>
       <c r="L17">
         <v>3.7614311754340659</v>
@@ -22523,7 +22523,7 @@
         <v>1410</v>
       </c>
       <c r="X17" t="s">
-        <v>1247</v>
+        <v>1238</v>
       </c>
       <c r="Y17">
         <v>42.080249999999999</v>
@@ -22558,7 +22558,7 @@
         <v>1274</v>
       </c>
       <c r="K18" t="s">
-        <v>1006</v>
+        <v>1022</v>
       </c>
       <c r="L18">
         <v>2.5731779960501728</v>
@@ -22591,7 +22591,7 @@
         <v>1412</v>
       </c>
       <c r="X18" t="s">
-        <v>1254</v>
+        <v>1216</v>
       </c>
       <c r="Y18">
         <v>19.922999999999998</v>
@@ -22626,7 +22626,7 @@
         <v>1276</v>
       </c>
       <c r="K19" t="s">
-        <v>1066</v>
+        <v>1103</v>
       </c>
       <c r="L19">
         <v>1.9040172385939969</v>
@@ -22659,7 +22659,7 @@
         <v>1414</v>
       </c>
       <c r="X19" t="s">
-        <v>1245</v>
+        <v>1236</v>
       </c>
       <c r="Y19">
         <v>51.427500000000002</v>
@@ -22694,7 +22694,7 @@
         <v>1278</v>
       </c>
       <c r="K20" t="s">
-        <v>1004</v>
+        <v>1020</v>
       </c>
       <c r="L20">
         <v>11.884376191048085</v>
@@ -22727,7 +22727,7 @@
         <v>1416</v>
       </c>
       <c r="X20" t="s">
-        <v>1219</v>
+        <v>1249</v>
       </c>
       <c r="Y20">
         <v>40.677</v>
@@ -22762,7 +22762,7 @@
         <v>1280</v>
       </c>
       <c r="K21" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="L21">
         <v>12.246676572623375</v>
@@ -22795,7 +22795,7 @@
         <v>1418</v>
       </c>
       <c r="X21" t="s">
-        <v>1236</v>
+        <v>1211</v>
       </c>
       <c r="Y21">
         <v>60.146250000000002</v>
@@ -22830,7 +22830,7 @@
         <v>1282</v>
       </c>
       <c r="K22" t="s">
-        <v>1071</v>
+        <v>1129</v>
       </c>
       <c r="L22">
         <v>11.221871479411517</v>
@@ -22863,7 +22863,7 @@
         <v>1420</v>
       </c>
       <c r="X22" t="s">
-        <v>1207</v>
+        <v>1250</v>
       </c>
       <c r="Y22">
         <v>39.273000000000003</v>
@@ -22898,7 +22898,7 @@
         <v>1284</v>
       </c>
       <c r="K23" t="s">
-        <v>1040</v>
+        <v>1061</v>
       </c>
       <c r="L23">
         <v>7.6463375414566821</v>
@@ -22931,7 +22931,7 @@
         <v>1422</v>
       </c>
       <c r="X23" t="s">
-        <v>1220</v>
+        <v>1228</v>
       </c>
       <c r="Y23">
         <v>44.889749999999999</v>
@@ -22966,7 +22966,7 @@
         <v>1286</v>
       </c>
       <c r="K24" t="s">
-        <v>1089</v>
+        <v>1036</v>
       </c>
       <c r="L24">
         <v>49.086666974214374</v>
@@ -22999,7 +22999,7 @@
         <v>1424</v>
       </c>
       <c r="X24" t="s">
-        <v>1237</v>
+        <v>1212</v>
       </c>
       <c r="Y24">
         <v>27.66375</v>
@@ -23034,7 +23034,7 @@
         <v>1288</v>
       </c>
       <c r="K25" t="s">
-        <v>1024</v>
+        <v>1006</v>
       </c>
       <c r="L25">
         <v>1.6757541426674882</v>
@@ -23067,7 +23067,7 @@
         <v>1426</v>
       </c>
       <c r="X25" t="s">
-        <v>1203</v>
+        <v>1232</v>
       </c>
       <c r="Y25">
         <v>21.581250000000001</v>
@@ -23102,7 +23102,7 @@
         <v>1290</v>
       </c>
       <c r="K26" t="s">
-        <v>1068</v>
+        <v>1105</v>
       </c>
       <c r="L26">
         <v>0.39959553615654331</v>
@@ -23135,7 +23135,7 @@
         <v>1428</v>
       </c>
       <c r="X26" t="s">
-        <v>1217</v>
+        <v>1247</v>
       </c>
       <c r="Y26">
         <v>56.094749999999998</v>
@@ -23170,7 +23170,7 @@
         <v>1292</v>
       </c>
       <c r="K27" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="L27">
         <v>1.7832075556426605</v>
@@ -23203,7 +23203,7 @@
         <v>1430</v>
       </c>
       <c r="X27" t="s">
-        <v>1234</v>
+        <v>1209</v>
       </c>
       <c r="Y27">
         <v>43.631999999999998</v>
@@ -23238,7 +23238,7 @@
         <v>1294</v>
       </c>
       <c r="K28" t="s">
-        <v>1014</v>
+        <v>1093</v>
       </c>
       <c r="L28">
         <v>0.35051099632091098</v>
@@ -23271,7 +23271,7 @@
         <v>1432</v>
       </c>
       <c r="X28" t="s">
-        <v>1224</v>
+        <v>1203</v>
       </c>
       <c r="Y28">
         <v>3.4402499999999998</v>
@@ -23306,7 +23306,7 @@
         <v>1296</v>
       </c>
       <c r="K29" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="L29">
         <v>5.5005105319204732</v>
@@ -23339,7 +23339,7 @@
         <v>1434</v>
       </c>
       <c r="X29" t="s">
-        <v>1211</v>
+        <v>1243</v>
       </c>
       <c r="Y29">
         <v>13.389749999999999</v>
@@ -23374,7 +23374,7 @@
         <v>1298</v>
       </c>
       <c r="K30" t="s">
-        <v>1094</v>
+        <v>1041</v>
       </c>
       <c r="L30">
         <v>0.34625959029864795</v>
@@ -23407,7 +23407,7 @@
         <v>1436</v>
       </c>
       <c r="X30" t="s">
-        <v>1251</v>
+        <v>1242</v>
       </c>
       <c r="Y30">
         <v>6.9757499999999997</v>
@@ -23442,7 +23442,7 @@
         <v>1300</v>
       </c>
       <c r="K31" t="s">
-        <v>1125</v>
+        <v>1077</v>
       </c>
       <c r="L31">
         <v>0.65440271382024695</v>
@@ -23475,7 +23475,7 @@
         <v>1438</v>
       </c>
       <c r="X31" t="s">
-        <v>1215</v>
+        <v>1226</v>
       </c>
       <c r="Y31">
         <v>38.154000000000003</v>
@@ -23510,7 +23510,7 @@
         <v>1302</v>
       </c>
       <c r="K32" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="L32">
         <v>0.5190595734350465</v>
@@ -23543,7 +23543,7 @@
         <v>1440</v>
       </c>
       <c r="X32" t="s">
-        <v>1249</v>
+        <v>1240</v>
       </c>
       <c r="Y32">
         <v>26.765999999999998</v>
@@ -23578,7 +23578,7 @@
         <v>1304</v>
       </c>
       <c r="K33" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="L33">
         <v>0.29505146981926272</v>
@@ -23611,7 +23611,7 @@
         <v>1442</v>
       </c>
       <c r="X33" t="s">
-        <v>1243</v>
+        <v>1224</v>
       </c>
       <c r="Y33">
         <v>35.325000000000003</v>
@@ -23646,7 +23646,7 @@
         <v>1306</v>
       </c>
       <c r="K34" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="L34">
         <v>0.28737649325389003</v>
@@ -23679,7 +23679,7 @@
         <v>1444</v>
       </c>
       <c r="X34" t="s">
-        <v>1252</v>
+        <v>1214</v>
       </c>
       <c r="Y34">
         <v>38.589750000000002</v>
@@ -23714,7 +23714,7 @@
         <v>1308</v>
       </c>
       <c r="K35" t="s">
-        <v>1042</v>
+        <v>1008</v>
       </c>
       <c r="L35">
         <v>0.85621181691755843</v>
@@ -23747,7 +23747,7 @@
         <v>1446</v>
       </c>
       <c r="X35" t="s">
-        <v>1230</v>
+        <v>1256</v>
       </c>
       <c r="Y35">
         <v>28.707000000000001</v>
@@ -23782,7 +23782,7 @@
         <v>1310</v>
       </c>
       <c r="K36" t="s">
-        <v>1038</v>
+        <v>1059</v>
       </c>
       <c r="L36">
         <v>2.2628760328229185</v>
@@ -23815,7 +23815,7 @@
         <v>1448</v>
       </c>
       <c r="X36" t="s">
-        <v>1226</v>
+        <v>1205</v>
       </c>
       <c r="Y36">
         <v>2.6655000000000002</v>
@@ -23850,7 +23850,7 @@
         <v>1312</v>
       </c>
       <c r="K37" t="s">
-        <v>1092</v>
+        <v>1039</v>
       </c>
       <c r="L37">
         <v>0.43370118574988076</v>
@@ -23883,7 +23883,7 @@
         <v>1450</v>
       </c>
       <c r="X37" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="Y37">
         <v>11.651999999999999</v>
@@ -23918,7 +23918,7 @@
         <v>1314</v>
       </c>
       <c r="K38" t="s">
-        <v>1123</v>
+        <v>1075</v>
       </c>
       <c r="L38">
         <v>2.5150267058852811</v>
@@ -23951,7 +23951,7 @@
         <v>1452</v>
       </c>
       <c r="X38" t="s">
-        <v>1256</v>
+        <v>1218</v>
       </c>
       <c r="Y38">
         <v>10.619249999999999</v>
@@ -23986,7 +23986,7 @@
         <v>1316</v>
       </c>
       <c r="K39" t="s">
-        <v>1046</v>
+        <v>1012</v>
       </c>
       <c r="L39">
         <v>2.2677057834637031</v>
@@ -24019,7 +24019,7 @@
         <v>1454</v>
       </c>
       <c r="X39" t="s">
-        <v>1241</v>
+        <v>1222</v>
       </c>
       <c r="Y39">
         <v>21.260999999999999</v>
@@ -24054,7 +24054,7 @@
         <v>1318</v>
       </c>
       <c r="K40" t="s">
-        <v>1026</v>
+        <v>1063</v>
       </c>
       <c r="L40">
         <v>4.0509443596880574</v>
@@ -24087,7 +24087,7 @@
         <v>1456</v>
       </c>
       <c r="X40" t="s">
-        <v>1228</v>
+        <v>1207</v>
       </c>
       <c r="Y40">
         <v>1.7955000000000001</v>
@@ -24122,7 +24122,7 @@
         <v>1320</v>
       </c>
       <c r="K41" t="s">
-        <v>1012</v>
+        <v>1091</v>
       </c>
       <c r="L41">
         <v>2.4836923620575391</v>
@@ -24155,7 +24155,7 @@
         <v>1458</v>
       </c>
       <c r="X41" t="s">
-        <v>1205</v>
+        <v>1234</v>
       </c>
       <c r="Y41">
         <v>26.880749999999999</v>
@@ -24190,7 +24190,7 @@
         <v>1322</v>
       </c>
       <c r="K42" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="L42">
         <v>2.885493974180005</v>
@@ -24225,7 +24225,7 @@
         <v>1324</v>
       </c>
       <c r="K43" t="s">
-        <v>1022</v>
+        <v>1004</v>
       </c>
       <c r="L43">
         <v>4.0763322608214585</v>
@@ -24260,7 +24260,7 @@
         <v>1326</v>
       </c>
       <c r="K44" t="s">
-        <v>1032</v>
+        <v>1069</v>
       </c>
       <c r="L44">
         <v>23.427729543154012</v>
@@ -24295,7 +24295,7 @@
         <v>1328</v>
       </c>
       <c r="K45" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="L45">
         <v>1.4999429400795936</v>
@@ -24330,7 +24330,7 @@
         <v>1330</v>
       </c>
       <c r="K46" t="s">
-        <v>1108</v>
+        <v>1126</v>
       </c>
       <c r="L46">
         <v>55.863958629218203</v>
@@ -24365,7 +24365,7 @@
         <v>1332</v>
       </c>
       <c r="K47" t="s">
-        <v>1098</v>
+        <v>1045</v>
       </c>
       <c r="L47">
         <v>17.068804920122925</v>
@@ -24400,7 +24400,7 @@
         <v>1334</v>
       </c>
       <c r="K48" t="s">
-        <v>1137</v>
+        <v>1034</v>
       </c>
       <c r="L48">
         <v>13.001084297219549</v>
@@ -24435,7 +24435,7 @@
         <v>1336</v>
       </c>
       <c r="K49" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="L49">
         <v>3.0756142181007986</v>
@@ -24470,7 +24470,7 @@
         <v>1338</v>
       </c>
       <c r="K50" t="s">
-        <v>1079</v>
+        <v>1137</v>
       </c>
       <c r="L50">
         <v>17.749707845203876</v>
@@ -24505,7 +24505,7 @@
         <v>1340</v>
       </c>
       <c r="K51" t="s">
-        <v>1131</v>
+        <v>1028</v>
       </c>
       <c r="L51">
         <v>2.3372365278937242</v>
@@ -24540,7 +24540,7 @@
         <v>1342</v>
       </c>
       <c r="K52" t="s">
-        <v>1030</v>
+        <v>1067</v>
       </c>
       <c r="L52">
         <v>4.2648673086521249</v>
@@ -24575,7 +24575,7 @@
         <v>1344</v>
       </c>
       <c r="K53" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="L53">
         <v>2.8571480649629004</v>
@@ -24610,7 +24610,7 @@
         <v>1346</v>
       </c>
       <c r="K54" t="s">
-        <v>1036</v>
+        <v>1073</v>
       </c>
       <c r="L54">
         <v>9.5169217846211289</v>
@@ -24645,7 +24645,7 @@
         <v>1348</v>
       </c>
       <c r="K55" t="s">
-        <v>1020</v>
+        <v>1099</v>
       </c>
       <c r="L55">
         <v>33.414563514376454</v>
@@ -24680,7 +24680,7 @@
         <v>1350</v>
       </c>
       <c r="K56" t="s">
-        <v>1129</v>
+        <v>1081</v>
       </c>
       <c r="L56">
         <v>18.904558868579112</v>
@@ -24715,7 +24715,7 @@
         <v>1352</v>
       </c>
       <c r="K57" t="s">
-        <v>1100</v>
+        <v>1047</v>
       </c>
       <c r="L57">
         <v>15.478330347836801</v>
@@ -24750,7 +24750,7 @@
         <v>1354</v>
       </c>
       <c r="K58" t="s">
-        <v>1070</v>
+        <v>1128</v>
       </c>
       <c r="L58">
         <v>14.176079891703212</v>
@@ -24785,7 +24785,7 @@
         <v>1356</v>
       </c>
       <c r="K59" t="s">
-        <v>1034</v>
+        <v>1071</v>
       </c>
       <c r="L59">
         <v>0.80973624203950822</v>
@@ -24820,7 +24820,7 @@
         <v>1358</v>
       </c>
       <c r="K60" t="s">
-        <v>1018</v>
+        <v>1097</v>
       </c>
       <c r="L60">
         <v>3.2067222321080848</v>
@@ -24855,7 +24855,7 @@
         <v>1360</v>
       </c>
       <c r="K61" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="L61">
         <v>0.66271354737797783</v>
@@ -24890,7 +24890,7 @@
         <v>1362</v>
       </c>
       <c r="K62" t="s">
-        <v>1077</v>
+        <v>1135</v>
       </c>
       <c r="L62">
         <v>1.8183767824138508</v>
@@ -24925,7 +24925,7 @@
         <v>1364</v>
       </c>
       <c r="K63" t="s">
-        <v>1028</v>
+        <v>1065</v>
       </c>
       <c r="L63">
         <v>0.24904319237866104</v>
@@ -24960,7 +24960,7 @@
         <v>1366</v>
       </c>
       <c r="K64" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="L64">
         <v>8.2047875916663029E-2</v>
@@ -24995,7 +24995,7 @@
         <v>1368</v>
       </c>
       <c r="K65" t="s">
-        <v>1050</v>
+        <v>1016</v>
       </c>
       <c r="L65">
         <v>11.861012832193515</v>
@@ -25030,7 +25030,7 @@
         <v>1370</v>
       </c>
       <c r="K66" t="s">
-        <v>1008</v>
+        <v>1024</v>
       </c>
       <c r="L66">
         <v>0.74143826937354373</v>
@@ -25065,7 +25065,7 @@
         <v>1372</v>
       </c>
       <c r="K67" t="s">
-        <v>1075</v>
+        <v>1133</v>
       </c>
       <c r="L67">
         <v>5.5201095579611916</v>
@@ -25100,7 +25100,7 @@
         <v>1374</v>
       </c>
       <c r="K68" t="s">
-        <v>1135</v>
+        <v>1032</v>
       </c>
       <c r="L68">
         <v>6.8285247240880329</v>
@@ -25135,7 +25135,7 @@
         <v>1376</v>
       </c>
       <c r="K69" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="L69">
         <v>14.065249575687433</v>
@@ -25170,7 +25170,7 @@
         <v>1378</v>
       </c>
       <c r="K70" t="s">
-        <v>1052</v>
+        <v>1018</v>
       </c>
       <c r="L70">
         <v>9.3799037679336319</v>
@@ -25205,7 +25205,7 @@
         <v>1380</v>
       </c>
       <c r="K71" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="L71">
         <v>42.785830383290261</v>
@@ -25240,7 +25240,7 @@
         <v>1382</v>
       </c>
       <c r="K72" t="s">
-        <v>1096</v>
+        <v>1043</v>
       </c>
       <c r="L72">
         <v>7.8693705940085819</v>
@@ -25275,7 +25275,7 @@
         <v>1384</v>
       </c>
       <c r="K73" t="s">
-        <v>1010</v>
+        <v>1026</v>
       </c>
       <c r="L73">
         <v>19.787589902082505</v>
@@ -25310,7 +25310,7 @@
         <v>1386</v>
       </c>
       <c r="K74" t="s">
-        <v>1127</v>
+        <v>1079</v>
       </c>
       <c r="L74">
         <v>18.319832830101969</v>
@@ -25345,7 +25345,7 @@
         <v>1388</v>
       </c>
       <c r="K75" t="s">
-        <v>1016</v>
+        <v>1095</v>
       </c>
       <c r="L75">
         <v>6.7551756478058005</v>
@@ -25380,7 +25380,7 @@
         <v>1390</v>
       </c>
       <c r="K76" t="s">
-        <v>1104</v>
+        <v>1122</v>
       </c>
       <c r="L76">
         <v>0.78969451031655336</v>
@@ -25415,7 +25415,7 @@
         <v>1392</v>
       </c>
       <c r="K77" t="s">
-        <v>1133</v>
+        <v>1030</v>
       </c>
       <c r="L77">
         <v>3.5275797249830152</v>
@@ -25450,7 +25450,7 @@
         <v>1394</v>
       </c>
       <c r="K78" t="s">
-        <v>1106</v>
+        <v>1124</v>
       </c>
       <c r="L78">
         <v>0.89663971235601181</v>
@@ -25485,7 +25485,7 @@
         <v>1396</v>
       </c>
       <c r="K79" t="s">
-        <v>1073</v>
+        <v>1131</v>
       </c>
       <c r="L79">
         <v>5.9305458091691294</v>
@@ -25500,7 +25500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6607D849-9B5D-47B3-B863-6BD0C45EA837}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B76999-FFB3-4BDB-A018-B08F138C51C0}">
   <dimension ref="B9:P61"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -26969,7 +26969,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7C00395-2043-4BEF-8645-5D601881C34D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1685DB2D-F5DD-44F9-A21D-30BDFC7DFCF0}">
   <dimension ref="B2:M45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_BRA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BRA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{101426D3-1019-4171-95E9-21BEBA6295C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38568ACD-CF88-466D-B00B-8DD2CB066F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5286" uniqueCount="1606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5286" uniqueCount="1607">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -4947,6 +4947,9 @@
   <si>
     <t>Transformer: e_w94745966-500 → e_w94745966-525</t>
   </si>
+  <si>
+    <t>e_BR15-500,e_BR20-500,e_BR258-500,e_BR303-230,e_BR305-230,e_BR340-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR63-500,e_BR644-500,e_BR683-500,e_BR689-500,e_BR691-500,e_BR777-500,e_BR803-500,e_BR851-500,e_BR862-500,e_r9328495-500,e_w108224468-500,e_w1090304792-500,e_w287393618-500,e_w32300871-500,e_w32300871-525,e_w32300871-765,e_w525253078-500</t>
+  </si>
 </sst>
 </file>
 
@@ -4960,7 +4963,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5108,15 +5111,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5208,11 +5204,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -5427,7 +5418,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -5447,9 +5438,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -5841,7 +5831,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5861,9 +5850,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="20">
+  <cellStyles count="19">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
-    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -6839,7 +6827,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_BR15-500,e_BR20-500,e_BR258-500,e_BR303-230,e_BR305-230,e_BR340-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR63-500,e_BR644-500,e_BR683-500,e_BR689-500,e_BR691-500,e_BR777-500,e_BR803-500,e_BR851-500,e_BR862-500,e_r9328495-500,e_w108224468-500,e_w1090304792-500,e_w287393618-500,e_w32300871-500,e_w32300871-525,e_w32300871-765,e_w525253078-500</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -6861,7 +6849,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_BR15-500,e_BR20-500,e_BR258-500,e_BR303-230,e_BR305-230,e_BR340-500,e_BR37-500,e_BR41-500,e_BR42-500,e_BR63-500,e_BR644-500,e_BR683-500,e_BR689-500,e_BR691-500,e_BR777-500,e_BR803-500,e_BR851-500,e_BR862-500,e_r9328495-500,e_w108224468-500,e_w1090304792-500,e_w287393618-500,e_w32300871-500,e_w32300871-525,e_w32300871-765,e_w525253078-500</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -6875,8 +6863,8 @@
       <c r="S28">
         <v>50</v>
       </c>
-      <c r="V28" s="147" t="s">
-        <v>19</v>
+      <c r="V28" t="s">
+        <v>1606</v>
       </c>
     </row>
   </sheetData>
@@ -8422,25 +8410,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="147" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149" t="s">
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="148"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="148" t="s">
+      <c r="G1" s="147"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="147" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="151" t="s">
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="150" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -8486,7 +8474,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="152"/>
+      <c r="O2" s="151"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -8531,7 +8519,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="152"/>
+      <c r="O3" s="151"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -8573,7 +8561,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="153"/>
+      <c r="O4" s="152"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
